--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H15" s="15">
-        <v>-11.764705882352</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
         <v>17</v>
       </c>
       <c r="J15" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K15" s="15">
-        <v>-39.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>6.25</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M15" s="15">
-        <v>6.25</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="N15" s="15">
-        <v>-65.306122448979</v>
+        <v>-70.175438596491</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D16" s="14">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="F16" s="14">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G16" s="14">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H16" s="15">
-        <v>-32.575757575757</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="I16" s="14">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="J16" s="14">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.824175824175</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.096153846153</v>
+        <v>-35.146443514644</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.265625</v>
+        <v>-47.278911564625</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.725663716814</v>
+        <v>-86.683848797250</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D17" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E17" s="15">
-        <v>15.909090909090</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="F17" s="14">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G17" s="14">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>3.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="J17" s="14">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.119850187265</v>
+        <v>-4.113924050632</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.925170068027</v>
+        <v>-11.661807580174</v>
       </c>
       <c r="M17" s="15">
-        <v>36.898395721925</v>
+        <v>42.253521126760</v>
       </c>
       <c r="N17" s="15">
-        <v>-49.407114624505</v>
+        <v>-48.027444253859</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D18" s="14">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G18" s="14">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H18" s="15">
-        <v>-17.948717948717</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="J18" s="14">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="K18" s="15">
-        <v>-7.534246575342</v>
+        <v>-14.204545454545</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.571428571428</v>
+        <v>-4.430379746835</v>
       </c>
       <c r="M18" s="15">
-        <v>-26.630434782608</v>
+        <v>-28.095238095238</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.597972972973</v>
+        <v>-89.026162790697</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="D19" s="14">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E19" s="15">
-        <v>-4.545454545454</v>
+        <v>45</v>
       </c>
       <c r="F19" s="14">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G19" s="14">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.218905472636</v>
+        <v>-3.133159268929</v>
       </c>
       <c r="I19" s="14">
-        <v>531</v>
+        <v>645</v>
       </c>
       <c r="J19" s="14">
-        <v>559</v>
+        <v>639</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.008944543828</v>
+        <v>0.938967136150</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.928902627511</v>
+        <v>-14.569536423841</v>
       </c>
       <c r="M19" s="15">
-        <v>13.461538461538</v>
+        <v>22.159090909090</v>
       </c>
       <c r="N19" s="15">
-        <v>-54.654141759180</v>
+        <v>-52.608376193975</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>72.727272727272</v>
       </c>
       <c r="F20" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G20" s="14">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H20" s="15">
-        <v>-19.298245614035</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="I20" s="14">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="J20" s="14">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K20" s="15">
-        <v>-10.958904109589</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.418604651162</v>
+        <v>-21.495327102803</v>
       </c>
       <c r="M20" s="15">
-        <v>25</v>
+        <v>47.368421052631</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.902439024390</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="D21" s="17">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.787234042553</v>
+        <v>-1.415094339622</v>
       </c>
       <c r="F21" s="17">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="G21" s="17">
-        <v>907</v>
+        <v>879</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.356119073869</v>
+        <v>-10.011376564277</v>
       </c>
       <c r="I21" s="17">
-        <v>1139</v>
+        <v>1355</v>
       </c>
       <c r="J21" s="17">
-        <v>1259</v>
+        <v>1471</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.531374106433</v>
+        <v>-7.885791978246</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.409742120343</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.815699658703</v>
+        <v>1.726726726726</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.378351539225</v>
+        <v>-76.833646777226</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
+        <v>19</v>
+      </c>
+      <c r="G22" s="14">
         <v>21</v>
       </c>
-      <c r="G22" s="14">
-        <v>17</v>
-      </c>
       <c r="H22" s="15">
-        <v>23.529411764705</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I22" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J22" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L22" s="15">
-        <v>-37.5</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="M22" s="15">
-        <v>-16.666666666666</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D23" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E23" s="15">
-        <v>-28.571428571428</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F23" s="14">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G23" s="14">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H23" s="15">
-        <v>-35.964912280701</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="I23" s="14">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="J23" s="14">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="K23" s="15">
-        <v>-34.042553191489</v>
+        <v>-36.904761904761</v>
       </c>
       <c r="L23" s="15">
-        <v>-32.116788321167</v>
+        <v>-35.757575757575</v>
       </c>
       <c r="M23" s="15">
-        <v>16.25</v>
+        <v>10.416666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D24" s="14">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="E24" s="15">
-        <v>-29.054054054054</v>
+        <v>-22.302158273381</v>
       </c>
       <c r="F24" s="14">
-        <v>844</v>
+        <v>816</v>
       </c>
       <c r="G24" s="14">
-        <v>1174</v>
+        <v>1190</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.109028960817</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="I24" s="14">
-        <v>1191</v>
+        <v>1405</v>
       </c>
       <c r="J24" s="14">
-        <v>1521</v>
+        <v>1799</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.696252465483</v>
+        <v>-21.901056142301</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.745933384972</v>
+        <v>-6.644518272425</v>
       </c>
       <c r="M24" s="15">
-        <v>27.926960257787</v>
+        <v>32.048872180451</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D25" s="14">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E25" s="15">
-        <v>-51.219512195122</v>
+        <v>-47.337278106508</v>
       </c>
       <c r="F25" s="14">
-        <v>417</v>
+        <v>382</v>
       </c>
       <c r="G25" s="14">
-        <v>670</v>
+        <v>704</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.761194029850</v>
+        <v>-45.738636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>590</v>
+        <v>679</v>
       </c>
       <c r="J25" s="14">
-        <v>852</v>
+        <v>1021</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.751173708920</v>
+        <v>-33.496571988246</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.492753623188</v>
+        <v>-15.965346534653</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D26" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E26" s="15">
-        <v>24.657534246575</v>
+        <v>-2.531645569620</v>
       </c>
       <c r="F26" s="14">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G26" s="14">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H26" s="15">
-        <v>9.310344827586</v>
+        <v>11.072664359861</v>
       </c>
       <c r="I26" s="14">
-        <v>451</v>
+        <v>532</v>
       </c>
       <c r="J26" s="14">
-        <v>432</v>
+        <v>511</v>
       </c>
       <c r="K26" s="15">
-        <v>4.398148148148</v>
+        <v>4.109589041095</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.380952380952</v>
+        <v>-1.115241635687</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.258555133079</v>
+        <v>-10.588235294117</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F27" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G27" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H27" s="15">
-        <v>-10.526315789473</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J27" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K27" s="15">
-        <v>-40.625</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L27" s="15">
-        <v>-24</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E28" s="15">
-        <v>22.222222222222</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="F28" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G28" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H28" s="15">
-        <v>5.263157894736</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I28" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J28" s="14">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="K28" s="15">
-        <v>24</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L28" s="15">
-        <v>6.896551724137</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,39 +1476,39 @@
         <v>29</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" s="14">
         <v>8</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L29" s="15">
-        <v>-27.272727272727</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M29" s="15">
-        <v>-46.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.578947368421</v>
+        <v>-90.825688073394</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>2</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,31 +1517,31 @@
         <v>29</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J30" s="14">
         <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L30" s="15">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.134831460674</v>
+        <v>-91.262135922330</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,25 +1558,25 @@
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
         <v>5</v>
       </c>
       <c r="H31" s="15">
-        <v>-40</v>
+        <v>60</v>
       </c>
       <c r="I31" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>33.333333333333</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L31" s="15">
-        <v>-27.272727272727</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1607,32 +1607,32 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>2</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="E33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+        <v>-75</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>29</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,330 +890,330 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>6</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J15" s="14">
         <v>34</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="L15" s="15">
-        <v>-5.555555555555</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-19.047619047619</v>
+        <v>-16</v>
       </c>
       <c r="N15" s="15">
-        <v>-70.175438596491</v>
+        <v>-70.833333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D16" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E16" s="15">
-        <v>-45.714285714285</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G16" s="14">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H16" s="15">
-        <v>-34.615384615384</v>
+        <v>-38.759689922480</v>
       </c>
       <c r="I16" s="14">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="J16" s="14">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="K16" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.125506072874</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.146443514644</v>
+        <v>-38.356164383561</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.278911564625</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.683848797250</v>
+        <v>-86.394557823129</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D17" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.326530612244</v>
+        <v>-18.965517241379</v>
       </c>
       <c r="F17" s="14">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G17" s="14">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="H17" s="15">
-        <v>3.333333333333</v>
+        <v>-5.527638190954</v>
       </c>
       <c r="I17" s="14">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="J17" s="14">
-        <v>316</v>
+        <v>374</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.113924050632</v>
+        <v>-5.347593582887</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.661807580174</v>
+        <v>-8.762886597938</v>
       </c>
       <c r="M17" s="15">
-        <v>42.253521126760</v>
+        <v>43.902439024390</v>
       </c>
       <c r="N17" s="15">
-        <v>-48.027444253859</v>
+        <v>-46.766917293233</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D18" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E18" s="15">
-        <v>-53.333333333333</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="F18" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G18" s="14">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.642857142857</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="I18" s="14">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="J18" s="14">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.204545454545</v>
+        <v>-11.848341232227</v>
       </c>
       <c r="L18" s="15">
-        <v>-4.430379746835</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="M18" s="15">
-        <v>-28.095238095238</v>
+        <v>-23.140495867768</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.026162790697</v>
+        <v>-88.360450563204</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D19" s="14">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E19" s="15">
-        <v>45</v>
+        <v>3.260869565217</v>
       </c>
       <c r="F19" s="14">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G19" s="14">
         <v>383</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.133159268929</v>
+        <v>-2.088772845953</v>
       </c>
       <c r="I19" s="14">
-        <v>645</v>
+        <v>745</v>
       </c>
       <c r="J19" s="14">
-        <v>639</v>
+        <v>731</v>
       </c>
       <c r="K19" s="15">
-        <v>0.938967136150</v>
+        <v>1.915184678522</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.569536423841</v>
+        <v>-11.938534278959</v>
       </c>
       <c r="M19" s="15">
-        <v>22.159090909090</v>
+        <v>25.210084033613</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.608376193975</v>
+        <v>-51.748704663212</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>72.727272727272</v>
+        <v>70</v>
       </c>
       <c r="F20" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" s="14">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H20" s="15">
-        <v>-1.923076923076</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I20" s="14">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="J20" s="14">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>8.510638297872</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.495327102803</v>
+        <v>-21.538461538461</v>
       </c>
       <c r="M20" s="15">
-        <v>47.368421052631</v>
+        <v>72.881355932203</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.333333333333</v>
+        <v>-92.950932964754</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D21" s="17">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E21" s="18">
-        <v>-1.415094339622</v>
+        <v>-1.777777777777</v>
       </c>
       <c r="F21" s="17">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="G21" s="17">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.011376564277</v>
+        <v>-9.841628959276</v>
       </c>
       <c r="I21" s="17">
-        <v>1355</v>
+        <v>1588</v>
       </c>
       <c r="J21" s="17">
-        <v>1471</v>
+        <v>1696</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.885791978246</v>
+        <v>-6.367924528301</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.666666666666</v>
+        <v>-15.621679064824</v>
       </c>
       <c r="M21" s="18">
-        <v>1.726726726726</v>
+        <v>5.235255135851</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.833646777226</v>
+        <v>-76.298507462686</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F22" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>-9.523809523809</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I22" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J22" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K22" s="15">
-        <v>-6.451612903225</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="L22" s="15">
-        <v>-30.952380952381</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="M22" s="15">
-        <v>-12.121212121212</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E23" s="15">
-        <v>-55.555555555555</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F23" s="14">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G23" s="14">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H23" s="15">
-        <v>-37.735849056603</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="I23" s="14">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="J23" s="14">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="K23" s="15">
-        <v>-36.904761904761</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-35.757575757575</v>
+        <v>-31.891891891891</v>
       </c>
       <c r="M23" s="15">
-        <v>10.416666666666</v>
+        <v>11.504424778761</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D24" s="14">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.302158273381</v>
+        <v>-22.348484848484</v>
       </c>
       <c r="F24" s="14">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="G24" s="14">
-        <v>1190</v>
+        <v>1142</v>
       </c>
       <c r="H24" s="15">
-        <v>-31.428571428571</v>
+        <v>-29.859894921190</v>
       </c>
       <c r="I24" s="14">
-        <v>1405</v>
+        <v>1603</v>
       </c>
       <c r="J24" s="14">
-        <v>1799</v>
+        <v>2063</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.901056142301</v>
+        <v>-22.297624818225</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.644518272425</v>
+        <v>-6.748109365910</v>
       </c>
       <c r="M24" s="15">
-        <v>32.048872180451</v>
+        <v>34.254606365159</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="14">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.337278106508</v>
+        <v>-44.099378881987</v>
       </c>
       <c r="F25" s="14">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="G25" s="14">
-        <v>704</v>
+        <v>681</v>
       </c>
       <c r="H25" s="15">
-        <v>-45.738636363636</v>
+        <v>-46.549192364170</v>
       </c>
       <c r="I25" s="14">
-        <v>679</v>
+        <v>768</v>
       </c>
       <c r="J25" s="14">
-        <v>1021</v>
+        <v>1182</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.496571988246</v>
+        <v>-35.025380710659</v>
       </c>
       <c r="L25" s="15">
-        <v>-15.965346534653</v>
+        <v>-16.521739130434</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D26" s="14">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" s="15">
-        <v>-2.531645569620</v>
+        <v>21.794871794871</v>
       </c>
       <c r="F26" s="14">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="G26" s="14">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H26" s="15">
-        <v>11.072664359861</v>
+        <v>15.807560137457</v>
       </c>
       <c r="I26" s="14">
-        <v>532</v>
+        <v>626</v>
       </c>
       <c r="J26" s="14">
-        <v>511</v>
+        <v>589</v>
       </c>
       <c r="K26" s="15">
-        <v>4.109589041095</v>
+        <v>6.281833616298</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.115241635687</v>
+        <v>0.481540930979</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.588235294117</v>
+        <v>-9.537572254335</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>7</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-71.428571428571</v>
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I27" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J27" s="14">
         <v>39</v>
       </c>
       <c r="K27" s="15">
-        <v>-46.153846153846</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="L27" s="15">
-        <v>-22.222222222222</v>
+        <v>-21.875</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="15">
-        <v>-69.230769230769</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F28" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G28" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H28" s="15">
-        <v>-15.384615384615</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I28" s="14">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="J28" s="14">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="K28" s="15">
-        <v>4.761904761904</v>
+        <v>1.298701298701</v>
       </c>
       <c r="L28" s="15">
-        <v>4.761904761904</v>
+        <v>11.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="14">
         <v>8</v>
       </c>
       <c r="K29" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L29" s="15">
-        <v>-9.090909090909</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M29" s="15">
-        <v>-37.5</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.825688073394</v>
+        <v>-91.129032258064</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,54 +1508,54 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J30" s="14">
         <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L30" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M30" s="15">
-        <v>-40</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.262135922330</v>
+        <v>-91.452991452991</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>8</v>
@@ -1567,22 +1567,22 @@
         <v>60</v>
       </c>
       <c r="I31" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>116.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>18.181818181818</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1635,13 +1635,13 @@
         <v>-75</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>482</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>12041</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>6092</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>14267</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>13799</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>12028</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>59088</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -860,32 +860,32 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-90</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-98.181818181818</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>25</v>
       </c>
       <c r="F15" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G15" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H15" s="15">
-        <v>-47.058823529411</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I15" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J15" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K15" s="15">
-        <v>-38.235294117647</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>-16</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-70.833333333333</v>
+        <v>-64.102564102564</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D16" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E16" s="15">
-        <v>-13.333333333333</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F16" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G16" s="14">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H16" s="15">
-        <v>-38.759689922480</v>
+        <v>-30.894308943089</v>
       </c>
       <c r="I16" s="14">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="J16" s="14">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="K16" s="15">
-        <v>-27.125506072874</v>
+        <v>-26.690391459074</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.356164383561</v>
+        <v>-37.951807228915</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.945945945945</v>
+        <v>-43.406593406593</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.394557823129</v>
+        <v>-86.005434782608</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D17" s="14">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" s="15">
-        <v>-18.965517241379</v>
+        <v>3.389830508474</v>
       </c>
       <c r="F17" s="14">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="G17" s="14">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.527638190954</v>
+        <v>-1.428571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>354</v>
+        <v>419</v>
       </c>
       <c r="J17" s="14">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.347593582887</v>
+        <v>-3.233256351039</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.762886597938</v>
+        <v>-5.417607223476</v>
       </c>
       <c r="M17" s="15">
-        <v>43.902439024390</v>
+        <v>53.479853479853</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.766917293233</v>
+        <v>-44.868421052631</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D18" s="14">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E18" s="15">
-        <v>-5.714285714285</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F18" s="14">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G18" s="14">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.962962962963</v>
+        <v>-15.596330275229</v>
       </c>
       <c r="I18" s="14">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="J18" s="14">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.848341232227</v>
+        <v>-12.970711297071</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.060606060606</v>
+        <v>-14.40329218107</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.140495867768</v>
+        <v>-21.509433962264</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.360450563204</v>
+        <v>-88.489208633093</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D19" s="14">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="E19" s="15">
-        <v>3.260869565217</v>
+        <v>-6.542056074766</v>
       </c>
       <c r="F19" s="14">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="G19" s="14">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.088772845953</v>
+        <v>8.446866485013</v>
       </c>
       <c r="I19" s="14">
-        <v>745</v>
+        <v>849</v>
       </c>
       <c r="J19" s="14">
-        <v>731</v>
+        <v>838</v>
       </c>
       <c r="K19" s="15">
-        <v>1.915184678522</v>
+        <v>1.312649164677</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.938534278959</v>
+        <v>-14.501510574018</v>
       </c>
       <c r="M19" s="15">
-        <v>25.210084033613</v>
+        <v>23.043478260869</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.748704663212</v>
+        <v>-51.346704871060</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>70</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F20" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G20" s="14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H20" s="15">
-        <v>13.043478260869</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I20" s="14">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J20" s="14">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K20" s="15">
-        <v>8.510638297872</v>
+        <v>1.904761904761</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.538461538461</v>
+        <v>-26.712328767123</v>
       </c>
       <c r="M20" s="15">
-        <v>72.881355932203</v>
+        <v>69.841269841269</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.950932964754</v>
+        <v>-93.451652386780</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D21" s="17">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="E21" s="18">
-        <v>-1.777777777777</v>
+        <v>-11.522633744856</v>
       </c>
       <c r="F21" s="17">
-        <v>797</v>
+        <v>843</v>
       </c>
       <c r="G21" s="17">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.841628959276</v>
+        <v>-2.880184331797</v>
       </c>
       <c r="I21" s="17">
-        <v>1588</v>
+        <v>1818</v>
       </c>
       <c r="J21" s="17">
-        <v>1696</v>
+        <v>1939</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.367924528301</v>
+        <v>-6.240330067044</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.621679064824</v>
+        <v>-16.986301369863</v>
       </c>
       <c r="M21" s="18">
-        <v>5.235255135851</v>
+        <v>7.256637168141</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.298507462686</v>
+        <v>-75.923718712753</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G22" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H22" s="15">
-        <v>-13.043478260869</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I22" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J22" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K22" s="15">
-        <v>-20.512820512820</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L22" s="15">
-        <v>-32.608695652173</v>
+        <v>-35.849056603773</v>
       </c>
       <c r="M22" s="15">
-        <v>-18.421052631578</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>15</v>
       </c>
       <c r="D23" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E23" s="15">
-        <v>-28.571428571428</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="F23" s="14">
         <v>64</v>
       </c>
       <c r="G23" s="14">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H23" s="15">
-        <v>-37.254901960784</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I23" s="14">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="J23" s="14">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.547169811320</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.891891891891</v>
+        <v>-33.177570093457</v>
       </c>
       <c r="M23" s="15">
-        <v>11.504424778761</v>
+        <v>13.492063492063</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D24" s="14">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.348484848484</v>
+        <v>-23.188405797101</v>
       </c>
       <c r="F24" s="14">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="G24" s="14">
-        <v>1142</v>
+        <v>1114</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.859894921190</v>
+        <v>-25.224416517055</v>
       </c>
       <c r="I24" s="14">
-        <v>1603</v>
+        <v>1809</v>
       </c>
       <c r="J24" s="14">
-        <v>2063</v>
+        <v>2339</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.297624818225</v>
+        <v>-22.659256092347</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.748109365910</v>
+        <v>-8.358662613981</v>
       </c>
       <c r="M24" s="15">
-        <v>34.254606365159</v>
+        <v>36.838124054462</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D25" s="14">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E25" s="15">
-        <v>-44.099378881987</v>
+        <v>-27.210884353741</v>
       </c>
       <c r="F25" s="14">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G25" s="14">
-        <v>681</v>
+        <v>641</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.549192364170</v>
+        <v>-42.901716068642</v>
       </c>
       <c r="I25" s="14">
-        <v>768</v>
+        <v>874</v>
       </c>
       <c r="J25" s="14">
-        <v>1182</v>
+        <v>1329</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.025380710659</v>
+        <v>-34.236267870579</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.521739130434</v>
+        <v>-17.313150425733</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D26" s="14">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E26" s="15">
-        <v>21.794871794871</v>
+        <v>-14.117647058823</v>
       </c>
       <c r="F26" s="14">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G26" s="14">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="H26" s="15">
-        <v>15.807560137457</v>
+        <v>6.031746031746</v>
       </c>
       <c r="I26" s="14">
-        <v>626</v>
+        <v>697</v>
       </c>
       <c r="J26" s="14">
-        <v>589</v>
+        <v>674</v>
       </c>
       <c r="K26" s="15">
-        <v>6.281833616298</v>
+        <v>3.412462908011</v>
       </c>
       <c r="L26" s="15">
-        <v>0.481540930979</v>
+        <v>-0.712250712250</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.537572254335</v>
+        <v>-9.597924773022</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="D27" s="14">
+        <v>5</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G27" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H27" s="15">
-        <v>-36.842105263157</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J27" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K27" s="15">
-        <v>-35.897435897435</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="15">
-        <v>-21.875</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" s="14">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-14.285714285714</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G28" s="14">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H28" s="15">
-        <v>-21.739130434782</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J28" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K28" s="15">
-        <v>1.298701298701</v>
+        <v>10</v>
       </c>
       <c r="L28" s="15">
-        <v>11.428571428571</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-21.428571428571</v>
+        <v>-25</v>
       </c>
       <c r="M29" s="15">
-        <v>-38.888888888888</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.129032258064</v>
+        <v>-91.240875912408</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I30" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="L30" s="15">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M30" s="15">
-        <v>-41.176470588235</v>
+        <v>-45</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.452991452991</v>
+        <v>-91.538461538461</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H31" s="15">
-        <v>60</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I31" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K31" s="15">
-        <v>133.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>27.272727272727</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1617,22 +1617,22 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -864,10 +864,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -879,13 +879,13 @@
         <v>-80</v>
       </c>
       <c r="L14" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="M14" s="15">
         <v>-90</v>
       </c>
       <c r="N14" s="15">
-        <v>-98.181818181818</v>
+        <v>-98.387096774193</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,13 +893,13 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>12</v>
@@ -911,22 +911,22 @@
         <v>-7.692307692307</v>
       </c>
       <c r="I15" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J15" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K15" s="15">
-        <v>-26.315789473684</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L15" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>-6.666666666666</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N15" s="15">
-        <v>-64.102564102564</v>
+        <v>-65.517241379310</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E16" s="15">
-        <v>-35.294117647058</v>
+        <v>-53.488372093023</v>
       </c>
       <c r="F16" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G16" s="14">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="H16" s="15">
-        <v>-30.894308943089</v>
+        <v>-36.619718309859</v>
       </c>
       <c r="I16" s="14">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="J16" s="14">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="K16" s="15">
-        <v>-26.690391459074</v>
+        <v>-30.246913580246</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.951807228915</v>
+        <v>-39.733333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.406593406593</v>
+        <v>-44.607843137254</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.005434782608</v>
+        <v>-86.401925391095</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D17" s="14">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E17" s="15">
-        <v>3.389830508474</v>
+        <v>6.976744186046</v>
       </c>
       <c r="F17" s="14">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="G17" s="14">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.428571428571</v>
+        <v>-7.177033492822</v>
       </c>
       <c r="I17" s="14">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="J17" s="14">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.233256351039</v>
+        <v>-2.731092436974</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.417607223476</v>
+        <v>-8.858267716535</v>
       </c>
       <c r="M17" s="15">
-        <v>53.479853479853</v>
+        <v>47.452229299363</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.868421052631</v>
+        <v>-46.412037037037</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>25</v>
+      </c>
+      <c r="D18" s="14">
         <v>22</v>
       </c>
-      <c r="D18" s="14">
-        <v>28</v>
-      </c>
       <c r="E18" s="15">
-        <v>-21.428571428571</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F18" s="14">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G18" s="14">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H18" s="15">
-        <v>-15.596330275229</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I18" s="14">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="J18" s="14">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.970711297071</v>
+        <v>-9.961685823754</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.40329218107</v>
+        <v>-11.654135338345</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.509433962264</v>
+        <v>-18.118466898954</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.489208633093</v>
+        <v>-88.179074446680</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D19" s="14">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E19" s="15">
-        <v>-6.542056074766</v>
+        <v>8.196721311475</v>
       </c>
       <c r="F19" s="14">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="G19" s="14">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="H19" s="15">
-        <v>8.446866485013</v>
+        <v>11.221945137157</v>
       </c>
       <c r="I19" s="14">
-        <v>849</v>
+        <v>983</v>
       </c>
       <c r="J19" s="14">
-        <v>838</v>
+        <v>960</v>
       </c>
       <c r="K19" s="15">
-        <v>1.312649164677</v>
+        <v>2.395833333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.501510574018</v>
+        <v>-11.281588447653</v>
       </c>
       <c r="M19" s="15">
-        <v>23.043478260869</v>
+        <v>24.430379746835</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.346704871060</v>
+        <v>-49.692937563971</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-54.545454545454</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F20" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G20" s="14">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H20" s="15">
-        <v>9.090909090909</v>
+        <v>36.585365853658</v>
       </c>
       <c r="I20" s="14">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="J20" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K20" s="15">
-        <v>1.904761904761</v>
+        <v>6.140350877192</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.712328767123</v>
+        <v>-24.375</v>
       </c>
       <c r="M20" s="15">
-        <v>69.841269841269</v>
+        <v>72.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.451652386780</v>
+        <v>-93.344334433443</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D21" s="17">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.522633744856</v>
+        <v>-0.829875518672</v>
       </c>
       <c r="F21" s="17">
-        <v>843</v>
+        <v>894</v>
       </c>
       <c r="G21" s="17">
-        <v>868</v>
+        <v>922</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.880184331797</v>
+        <v>-3.036876355748</v>
       </c>
       <c r="I21" s="17">
-        <v>1818</v>
+        <v>2059</v>
       </c>
       <c r="J21" s="17">
-        <v>1939</v>
+        <v>2181</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.240330067044</v>
+        <v>-5.593764328289</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.986301369863</v>
+        <v>-15.993472052223</v>
       </c>
       <c r="M21" s="18">
-        <v>7.256637168141</v>
+        <v>7.688284518828</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.923718712753</v>
+        <v>-75.589804386484</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F22" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G22" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>-23.809523809523</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="I22" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J22" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K22" s="15">
-        <v>-19.047619047619</v>
+        <v>-18.75</v>
       </c>
       <c r="L22" s="15">
-        <v>-35.849056603773</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M22" s="15">
-        <v>-17.073170731707</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="14">
         <v>23</v>
       </c>
       <c r="E23" s="15">
-        <v>-34.782608695652</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="F23" s="14">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G23" s="14">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H23" s="15">
-        <v>-30.434782608695</v>
+        <v>-34.736842105263</v>
       </c>
       <c r="I23" s="14">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="J23" s="14">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="K23" s="15">
-        <v>-32.547169811320</v>
+        <v>-32.627118644067</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.177570093457</v>
+        <v>-34.567901234567</v>
       </c>
       <c r="M23" s="15">
-        <v>13.492063492063</v>
+        <v>8.163265306122</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D24" s="14">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.188405797101</v>
+        <v>-17.424242424242</v>
       </c>
       <c r="F24" s="14">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="G24" s="14">
-        <v>1114</v>
+        <v>1082</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.224416517055</v>
+        <v>-21.626617375231</v>
       </c>
       <c r="I24" s="14">
-        <v>1809</v>
+        <v>2023</v>
       </c>
       <c r="J24" s="14">
-        <v>2339</v>
+        <v>2603</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.659256092347</v>
+        <v>-22.281982328083</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.358662613981</v>
+        <v>-7.625570776255</v>
       </c>
       <c r="M24" s="15">
-        <v>36.838124054462</v>
+        <v>36.874154262516</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D25" s="14">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E25" s="15">
-        <v>-27.210884353741</v>
+        <v>-45.121951219512</v>
       </c>
       <c r="F25" s="14">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="G25" s="14">
         <v>641</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.901716068642</v>
+        <v>-41.341653666146</v>
       </c>
       <c r="I25" s="14">
-        <v>874</v>
+        <v>965</v>
       </c>
       <c r="J25" s="14">
-        <v>1329</v>
+        <v>1493</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.236267870579</v>
+        <v>-35.36503683858</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.313150425733</v>
+        <v>-15.940766550522</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D26" s="14">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E26" s="15">
-        <v>-14.117647058823</v>
+        <v>7.070707070707</v>
       </c>
       <c r="F26" s="14">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="G26" s="14">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="H26" s="15">
-        <v>6.031746031746</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I26" s="14">
-        <v>697</v>
+        <v>805</v>
       </c>
       <c r="J26" s="14">
-        <v>674</v>
+        <v>773</v>
       </c>
       <c r="K26" s="15">
-        <v>3.412462908011</v>
+        <v>4.139715394566</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.712250712250</v>
+        <v>0.124378109452</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.597924773022</v>
+        <v>-7.364787111622</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,13 +1385,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F27" s="14">
         <v>15</v>
@@ -1403,16 +1403,16 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J27" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K27" s="15">
-        <v>-25</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="L27" s="15">
-        <v>-10.810810810810</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>8</v>
+      </c>
+      <c r="D28" s="14">
         <v>13</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
       <c r="E28" s="15">
-        <v>333.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F28" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G28" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J28" s="14">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K28" s="15">
-        <v>10</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L28" s="15">
-        <v>4.761904761904</v>
+        <v>-4</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J29" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="L29" s="15">
-        <v>-25</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M29" s="15">
-        <v>-45.454545454545</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.240875912408</v>
+        <v>-90.728476821192</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-15.384615384615</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M30" s="15">
-        <v>-45</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.538461538461</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,34 +1549,34 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
+        <v>5</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
       <c r="E31" s="15">
-        <v>-66.666666666666</v>
+        <v>400</v>
       </c>
       <c r="F31" s="14">
+        <v>7</v>
+      </c>
+      <c r="G31" s="14">
         <v>6</v>
       </c>
-      <c r="G31" s="14">
-        <v>7</v>
-      </c>
       <c r="H31" s="15">
-        <v>-14.285714285714</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I31" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J31" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" s="15">
-        <v>66.666666666666</v>
+        <v>90</v>
       </c>
       <c r="L31" s="15">
-        <v>7.142857142857</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="14">
         <v>2</v>
       </c>
-      <c r="G33" s="14">
-        <v>2</v>
-      </c>
-      <c r="H33" s="15">
-        <v>0</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="15">
         <v>-50</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L14" s="15">
         <v>-90</v>
@@ -885,335 +885,335 @@
         <v>-90</v>
       </c>
       <c r="N14" s="15">
-        <v>-98.387096774193</v>
+        <v>-98.591549295774</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F15" s="14">
+        <v>16</v>
+      </c>
+      <c r="G15" s="14">
         <v>12</v>
       </c>
-      <c r="G15" s="14">
-        <v>13</v>
-      </c>
       <c r="H15" s="15">
-        <v>-7.692307692307</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J15" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K15" s="15">
-        <v>-26.829268292682</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M15" s="15">
-        <v>-9.090909090909</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N15" s="15">
-        <v>-65.517241379310</v>
+        <v>-60.869565217391</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D16" s="14">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E16" s="15">
-        <v>-53.488372093023</v>
+        <v>25.925925925925</v>
       </c>
       <c r="F16" s="14">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G16" s="14">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H16" s="15">
-        <v>-36.619718309859</v>
+        <v>-23.134328358209</v>
       </c>
       <c r="I16" s="14">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="J16" s="14">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="K16" s="15">
-        <v>-30.246913580246</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.733333333333</v>
+        <v>-35.960591133004</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.607843137254</v>
+        <v>-42.477876106194</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.401925391095</v>
+        <v>-85.729967069154</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D17" s="14">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E17" s="15">
-        <v>6.976744186046</v>
+        <v>6.896551724137</v>
       </c>
       <c r="F17" s="14">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="G17" s="14">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.177033492822</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>463</v>
+        <v>530</v>
       </c>
       <c r="J17" s="14">
-        <v>476</v>
+        <v>534</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.731092436974</v>
+        <v>-0.749063670411</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.858267716535</v>
+        <v>-8.620689655172</v>
       </c>
       <c r="M17" s="15">
-        <v>47.452229299363</v>
+        <v>52.737752161383</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.412037037037</v>
+        <v>-44.502617801047</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D18" s="14">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>13.636363636363</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="F18" s="14">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="G18" s="14">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H18" s="15">
-        <v>-17.391304347826</v>
+        <v>-5.084745762711</v>
       </c>
       <c r="I18" s="14">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="J18" s="14">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="K18" s="15">
-        <v>-9.961685823754</v>
+        <v>-8.843537414965</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.654135338345</v>
+        <v>-10.963455149501</v>
       </c>
       <c r="M18" s="15">
-        <v>-18.118466898954</v>
+        <v>-13.268608414239</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.179074446680</v>
+        <v>-87.784867821330</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="D19" s="14">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E19" s="15">
-        <v>8.196721311475</v>
+        <v>-13.6</v>
       </c>
       <c r="F19" s="14">
+        <v>438</v>
+      </c>
+      <c r="G19" s="14">
         <v>446</v>
       </c>
-      <c r="G19" s="14">
-        <v>401</v>
-      </c>
       <c r="H19" s="15">
-        <v>11.221945137157</v>
+        <v>-1.793721973094</v>
       </c>
       <c r="I19" s="14">
-        <v>983</v>
+        <v>1093</v>
       </c>
       <c r="J19" s="14">
-        <v>960</v>
+        <v>1085</v>
       </c>
       <c r="K19" s="15">
-        <v>2.395833333333</v>
+        <v>0.737327188940</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.281588447653</v>
+        <v>-11.712439418416</v>
       </c>
       <c r="M19" s="15">
-        <v>24.430379746835</v>
+        <v>24.914285714285</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.692937563971</v>
+        <v>-48.805620608899</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E20" s="15">
-        <v>55.555555555555</v>
+        <v>-6.25</v>
       </c>
       <c r="F20" s="14">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G20" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H20" s="15">
-        <v>36.585365853658</v>
+        <v>6.521739130434</v>
       </c>
       <c r="I20" s="14">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="J20" s="14">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K20" s="15">
-        <v>6.140350877192</v>
+        <v>3.076923076923</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.375</v>
+        <v>-26.775956284153</v>
       </c>
       <c r="M20" s="15">
-        <v>72.857142857142</v>
+        <v>63.414634146341</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.344334433443</v>
+        <v>-93.149284253578</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D21" s="17">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="E21" s="18">
-        <v>-0.829875518672</v>
+        <v>-4.150943396226</v>
       </c>
       <c r="F21" s="17">
-        <v>894</v>
+        <v>937</v>
       </c>
       <c r="G21" s="17">
-        <v>922</v>
+        <v>975</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.036876355748</v>
+        <v>-3.897435897435</v>
       </c>
       <c r="I21" s="17">
-        <v>2059</v>
+        <v>2322</v>
       </c>
       <c r="J21" s="17">
-        <v>2181</v>
+        <v>2446</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.593764328289</v>
+        <v>-5.069501226492</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.993472052223</v>
+        <v>-15.379008746355</v>
       </c>
       <c r="M21" s="18">
-        <v>7.688284518828</v>
+        <v>10.099573257468</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.589804386484</v>
+        <v>-74.829268292682</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="14">
         <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G22" s="14">
         <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>-39.130434782608</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I22" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J22" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K22" s="15">
-        <v>-18.75</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L22" s="15">
-        <v>-31.578947368421</v>
+        <v>-26.984126984127</v>
       </c>
       <c r="M22" s="15">
-        <v>-15.217391304347</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23" s="15">
-        <v>-39.130434782608</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G23" s="14">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H23" s="15">
-        <v>-34.736842105263</v>
+        <v>-27.173913043478</v>
       </c>
       <c r="I23" s="14">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="J23" s="14">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="K23" s="15">
-        <v>-32.627118644067</v>
+        <v>-30</v>
       </c>
       <c r="L23" s="15">
-        <v>-34.567901234567</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M23" s="15">
-        <v>8.163265306122</v>
+        <v>13.043478260869</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D24" s="14">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.424242424242</v>
+        <v>-9.2</v>
       </c>
       <c r="F24" s="14">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="G24" s="14">
-        <v>1082</v>
+        <v>1054</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.626617375231</v>
+        <v>-18.785578747628</v>
       </c>
       <c r="I24" s="14">
-        <v>2023</v>
+        <v>2247</v>
       </c>
       <c r="J24" s="14">
-        <v>2603</v>
+        <v>2853</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.281982328083</v>
+        <v>-21.240799158780</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.625570776255</v>
+        <v>-7.225433526011</v>
       </c>
       <c r="M24" s="15">
-        <v>36.874154262516</v>
+        <v>38.362068965517</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D25" s="14">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.121951219512</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="F25" s="14">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G25" s="14">
-        <v>641</v>
+        <v>607</v>
       </c>
       <c r="H25" s="15">
-        <v>-41.341653666146</v>
+        <v>-37.891268533772</v>
       </c>
       <c r="I25" s="14">
-        <v>965</v>
+        <v>1053</v>
       </c>
       <c r="J25" s="14">
-        <v>1493</v>
+        <v>1628</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.36503683858</v>
+        <v>-35.319410319410</v>
       </c>
       <c r="L25" s="15">
-        <v>-15.940766550522</v>
+        <v>-17.605633802816</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D26" s="14">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E26" s="15">
-        <v>7.070707070707</v>
+        <v>9.782608695652</v>
       </c>
       <c r="F26" s="14">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="G26" s="14">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="H26" s="15">
-        <v>3.225806451612</v>
+        <v>6.497175141242</v>
       </c>
       <c r="I26" s="14">
-        <v>805</v>
+        <v>905</v>
       </c>
       <c r="J26" s="14">
-        <v>773</v>
+        <v>865</v>
       </c>
       <c r="K26" s="15">
-        <v>4.139715394566</v>
+        <v>4.624277456647</v>
       </c>
       <c r="L26" s="15">
-        <v>0.124378109452</v>
+        <v>-0.110375275938</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.364787111622</v>
+        <v>-6.217616580310</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F27" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G27" s="14">
         <v>15</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J27" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K27" s="15">
-        <v>-23.404255319148</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>-7.692307692307</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,122 +1426,122 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E28" s="15">
-        <v>-38.461538461538</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G28" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I28" s="14">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="J28" s="14">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="K28" s="15">
-        <v>4.347826086956</v>
+        <v>1.869158878504</v>
       </c>
       <c r="L28" s="15">
-        <v>-4</v>
+        <v>0.925925925925</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>3</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>14</v>
       </c>
       <c r="J29" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" s="15">
-        <v>40</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L29" s="15">
-        <v>-17.647058823529</v>
+        <v>-30</v>
       </c>
       <c r="M29" s="15">
-        <v>-39.130434782608</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.728476821192</v>
+        <v>-91.566265060241</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I30" s="14">
         <v>12</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="L30" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.156862745098</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,40 +1549,40 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" s="14">
         <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31" s="15">
-        <v>16.666666666666</v>
+        <v>60</v>
       </c>
       <c r="I31" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K31" s="15">
-        <v>90</v>
+        <v>81.818181818181</v>
       </c>
       <c r="L31" s="15">
-        <v>11.764705882352</v>
+        <v>17.647058823529</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1638,10 +1638,10 @@
         <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>482</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>12041</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>6092</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>14267</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>13799</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>12028</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>59088</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -870,350 +870,350 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-90</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="M14" s="15">
-        <v>-90</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N14" s="15">
-        <v>-98.591549295774</v>
+        <v>-97.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H15" s="15">
-        <v>33.333333333333</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J15" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K15" s="15">
-        <v>-21.739130434782</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
-        <v>38.461538461538</v>
+        <v>53.846153846153</v>
       </c>
       <c r="M15" s="15">
-        <v>5.882352941176</v>
+        <v>5.263157894736</v>
       </c>
       <c r="N15" s="15">
-        <v>-60.869565217391</v>
+        <v>-59.595959595959</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="15">
-        <v>25.925925925925</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F16" s="14">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16" s="14">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.134328358209</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="14">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="J16" s="14">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.925925925925</v>
+        <v>-23.342175066313</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.960591133004</v>
+        <v>-35.201793721973</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.477876106194</v>
+        <v>-40.657084188911</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.729967069154</v>
+        <v>-85.571642536195</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D17" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E17" s="15">
-        <v>6.896551724137</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F17" s="14">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="G17" s="14">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>4.035874439461</v>
       </c>
       <c r="I17" s="14">
-        <v>530</v>
+        <v>596</v>
       </c>
       <c r="J17" s="14">
-        <v>534</v>
+        <v>597</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.749063670411</v>
+        <v>-0.167504187604</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.620689655172</v>
+        <v>-8.448540706605</v>
       </c>
       <c r="M17" s="15">
-        <v>52.737752161383</v>
+        <v>54.805194805194</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.502617801047</v>
+        <v>-43.075453677172</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D18" s="14">
         <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>-6.060606060606</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="F18" s="14">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="G18" s="14">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.084745762711</v>
+        <v>-16.379310344827</v>
       </c>
       <c r="I18" s="14">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="J18" s="14">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="K18" s="15">
-        <v>-8.843537414965</v>
+        <v>-12.844036697247</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.963455149501</v>
+        <v>-13.109756097561</v>
       </c>
       <c r="M18" s="15">
-        <v>-13.268608414239</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.784867821330</v>
+        <v>-88.095238095238</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D19" s="14">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E19" s="15">
-        <v>-13.6</v>
+        <v>-21.985815602836</v>
       </c>
       <c r="F19" s="14">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="G19" s="14">
-        <v>446</v>
+        <v>495</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.793721973094</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>1093</v>
+        <v>1203</v>
       </c>
       <c r="J19" s="14">
-        <v>1085</v>
+        <v>1226</v>
       </c>
       <c r="K19" s="15">
-        <v>0.737327188940</v>
+        <v>-1.876019575856</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.712439418416</v>
+        <v>-13.203463203463</v>
       </c>
       <c r="M19" s="15">
-        <v>24.914285714285</v>
+        <v>26.631578947368</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.805620608899</v>
+        <v>-48.413379073756</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E20" s="15">
-        <v>-6.25</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="F20" s="14">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G20" s="14">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="H20" s="15">
-        <v>6.521739130434</v>
+        <v>-30.508474576271</v>
       </c>
       <c r="I20" s="14">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="J20" s="14">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="K20" s="15">
-        <v>3.076923076923</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.775956284153</v>
+        <v>-28.358208955223</v>
       </c>
       <c r="M20" s="15">
-        <v>63.414634146341</v>
+        <v>65.517241379310</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.149284253578</v>
+        <v>-93.175355450237</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="D21" s="17">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.150943396226</v>
+        <v>-19.655172413793</v>
       </c>
       <c r="F21" s="17">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="G21" s="17">
-        <v>975</v>
+        <v>1039</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.897435897435</v>
+        <v>-9.432146294513</v>
       </c>
       <c r="I21" s="17">
-        <v>2322</v>
+        <v>2559</v>
       </c>
       <c r="J21" s="17">
-        <v>2446</v>
+        <v>2736</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.069501226492</v>
+        <v>-6.469298245614</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.379008746355</v>
+        <v>-16.070842899311</v>
       </c>
       <c r="M21" s="18">
-        <v>10.099573257468</v>
+        <v>12.187637001315</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.829268292682</v>
+        <v>-74.562624254473</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F22" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G22" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H22" s="15">
-        <v>-26.086956521739</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J22" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K22" s="15">
-        <v>-14.814814814814</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="L22" s="15">
-        <v>-26.984126984127</v>
+        <v>-22.058823529411</v>
       </c>
       <c r="M22" s="15">
-        <v>-4.166666666666</v>
+        <v>3.921568627450</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D23" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E23" s="15">
-        <v>-16.666666666666</v>
+        <v>22.580645161290</v>
       </c>
       <c r="F23" s="14">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G23" s="14">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H23" s="15">
-        <v>-27.173913043478</v>
+        <v>-11.881188118811</v>
       </c>
       <c r="I23" s="14">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="J23" s="14">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="K23" s="15">
-        <v>-30</v>
+        <v>-24.054982817869</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.578947368421</v>
+        <v>-22.183098591549</v>
       </c>
       <c r="M23" s="15">
-        <v>13.043478260869</v>
+        <v>26.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="D24" s="14">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.2</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="F24" s="14">
-        <v>856</v>
+        <v>917</v>
       </c>
       <c r="G24" s="14">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.785578747628</v>
+        <v>-13.162878787878</v>
       </c>
       <c r="I24" s="14">
-        <v>2247</v>
+        <v>2507</v>
       </c>
       <c r="J24" s="14">
-        <v>2853</v>
+        <v>3119</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.240799158780</v>
+        <v>-19.621673613337</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.225433526011</v>
+        <v>-6.350392230108</v>
       </c>
       <c r="M24" s="15">
-        <v>38.362068965517</v>
+        <v>41.319052987598</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="D25" s="14">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.555555555555</v>
+        <v>-27.647058823529</v>
       </c>
       <c r="F25" s="14">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="G25" s="14">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.891268533772</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="I25" s="14">
-        <v>1053</v>
+        <v>1174</v>
       </c>
       <c r="J25" s="14">
-        <v>1628</v>
+        <v>1798</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.319410319410</v>
+        <v>-34.705228031145</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.605633802816</v>
+        <v>-16.022889842632</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D26" s="14">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E26" s="15">
-        <v>9.782608695652</v>
+        <v>10.810810810810</v>
       </c>
       <c r="F26" s="14">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G26" s="14">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H26" s="15">
-        <v>6.497175141242</v>
+        <v>4.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>905</v>
+        <v>985</v>
       </c>
       <c r="J26" s="14">
-        <v>865</v>
+        <v>939</v>
       </c>
       <c r="K26" s="15">
-        <v>4.624277456647</v>
+        <v>4.898828541001</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.110375275938</v>
+        <v>-1.598401598401</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.217616580310</v>
+        <v>-9.715857011915</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1388,37 +1388,37 @@
         <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>-42.857142857142</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
         <v>17</v>
       </c>
       <c r="G27" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H27" s="15">
-        <v>13.333333333333</v>
+        <v>-15</v>
       </c>
       <c r="I27" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J27" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K27" s="15">
-        <v>-22.222222222222</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-2.325581395348</v>
+        <v>6.976744186046</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D28" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F28" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G28" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H28" s="15">
-        <v>4.545454545454</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I28" s="14">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="J28" s="14">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="K28" s="15">
-        <v>1.869158878504</v>
+        <v>2.479338842975</v>
       </c>
       <c r="L28" s="15">
-        <v>0.925925925925</v>
+        <v>-2.362204724409</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F29" s="14">
         <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I29" s="14">
+        <v>15</v>
+      </c>
+      <c r="J29" s="14">
         <v>14</v>
       </c>
-      <c r="J29" s="14">
-        <v>11</v>
-      </c>
       <c r="K29" s="15">
-        <v>27.272727272727</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L29" s="15">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="M29" s="15">
-        <v>-46.153846153846</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.566265060241</v>
+        <v>-91.477272727272</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F30" s="14">
         <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J30" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K30" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-25</v>
+        <v>-18.75</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-60.606060606060</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.156862745098</v>
+        <v>-92.024539877300</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
+        <v>7</v>
+      </c>
+      <c r="G31" s="14">
         <v>8</v>
       </c>
-      <c r="G31" s="14">
-        <v>5</v>
-      </c>
       <c r="H31" s="15">
-        <v>60</v>
+        <v>-12.5</v>
       </c>
       <c r="I31" s="14">
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K31" s="15">
-        <v>81.818181818181</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L31" s="15">
-        <v>17.647058823529</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="14">
         <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L33" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>482</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>12041</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>6092</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>14267</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>13799</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>12028</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>59088</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -879,13 +879,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-81.818181818181</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="M14" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-97.333333333333</v>
+        <v>-97.560975609756</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>13</v>
+      </c>
+      <c r="G15" s="14">
+        <v>13</v>
+      </c>
+      <c r="H15" s="15">
         <v>0</v>
       </c>
-      <c r="F15" s="14">
-        <v>16</v>
-      </c>
-      <c r="G15" s="14">
-        <v>15</v>
-      </c>
-      <c r="H15" s="15">
-        <v>6.666666666666</v>
-      </c>
       <c r="I15" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J15" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="L15" s="15">
-        <v>53.846153846153</v>
+        <v>48.275862068965</v>
       </c>
       <c r="M15" s="15">
-        <v>5.263157894736</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="N15" s="15">
-        <v>-59.595959595959</v>
+        <v>-59.047619047619</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D16" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E16" s="15">
-        <v>23.076923076923</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G16" s="14">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H16" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="J16" s="14">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.342175066313</v>
+        <v>-23.587223587223</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.201793721973</v>
+        <v>-36.40081799591</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.657084188911</v>
+        <v>-41.977611940298</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.571642536195</v>
+        <v>-85.740486015589</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D17" s="14">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E17" s="15">
-        <v>-4.761904761904</v>
+        <v>-26.785714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G17" s="14">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H17" s="15">
-        <v>4.035874439461</v>
+        <v>1.363636363636</v>
       </c>
       <c r="I17" s="14">
-        <v>596</v>
+        <v>646</v>
       </c>
       <c r="J17" s="14">
-        <v>597</v>
+        <v>653</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.167504187604</v>
+        <v>-1.071975497702</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.448540706605</v>
+        <v>-8.238636363636</v>
       </c>
       <c r="M17" s="15">
-        <v>54.805194805194</v>
+        <v>57.177615571776</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.075453677172</v>
+        <v>-44.927536231884</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E18" s="15">
-        <v>-48.484848484848</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F18" s="14">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G18" s="14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.379310344827</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="I18" s="14">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="J18" s="14">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.844036697247</v>
+        <v>-13.483146067415</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.109756097561</v>
+        <v>-13.239436619718</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.764705882352</v>
+        <v>-10.465116279069</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.095238095238</v>
+        <v>-88.144726712856</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D19" s="14">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.985815602836</v>
+        <v>1.960784313725</v>
       </c>
       <c r="F19" s="14">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G19" s="14">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.090909090909</v>
+        <v>-7.551020408163</v>
       </c>
       <c r="I19" s="14">
-        <v>1203</v>
+        <v>1305</v>
       </c>
       <c r="J19" s="14">
-        <v>1226</v>
+        <v>1328</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.876019575856</v>
+        <v>-1.731927710843</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.203463203463</v>
+        <v>-11.943319838056</v>
       </c>
       <c r="M19" s="15">
-        <v>26.631578947368</v>
+        <v>26.576139670223</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.413379073756</v>
+        <v>-48.803452334248</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E20" s="15">
-        <v>-56.521739130434</v>
+        <v>-40</v>
       </c>
       <c r="F20" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G20" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H20" s="15">
-        <v>-30.508474576271</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I20" s="14">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J20" s="14">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.882352941176</v>
+        <v>-9.826589595375</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.358208955223</v>
+        <v>-28.767123287671</v>
       </c>
       <c r="M20" s="15">
-        <v>65.517241379310</v>
+        <v>57.575757575757</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.175355450237</v>
+        <v>-93.229166666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="D21" s="17">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.655172413793</v>
+        <v>-13.807531380753</v>
       </c>
       <c r="F21" s="17">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G21" s="17">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.432146294513</v>
+        <v>-9.275362318840</v>
       </c>
       <c r="I21" s="17">
-        <v>2559</v>
+        <v>2771</v>
       </c>
       <c r="J21" s="17">
-        <v>2736</v>
+        <v>2975</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.469298245614</v>
+        <v>-6.857142857142</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.070842899311</v>
+        <v>-15.851806863042</v>
       </c>
       <c r="M21" s="18">
-        <v>12.187637001315</v>
+        <v>11.778943122226</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.562624254473</v>
+        <v>-74.790756914119</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>7</v>
       </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
       <c r="E22" s="15">
-        <v>133.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H22" s="15">
-        <v>16.666666666666</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I22" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J22" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K22" s="15">
-        <v>-7.017543859649</v>
+        <v>-14.0625</v>
       </c>
       <c r="L22" s="15">
-        <v>-22.058823529411</v>
+        <v>-25.675675675675</v>
       </c>
       <c r="M22" s="15">
-        <v>3.921568627450</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D23" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E23" s="15">
-        <v>22.580645161290</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F23" s="14">
         <v>89</v>
       </c>
       <c r="G23" s="14">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H23" s="15">
-        <v>-11.881188118811</v>
+        <v>-14.423076923076</v>
       </c>
       <c r="I23" s="14">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="J23" s="14">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="K23" s="15">
-        <v>-24.054982817869</v>
+        <v>-25.236593059936</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.183098591549</v>
+        <v>-24.038461538461</v>
       </c>
       <c r="M23" s="15">
-        <v>26.285714285714</v>
+        <v>22.164948453608</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D24" s="14">
-        <v>266</v>
+        <v>315</v>
       </c>
       <c r="E24" s="15">
-        <v>-2.631578947368</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F24" s="14">
-        <v>917</v>
+        <v>959</v>
       </c>
       <c r="G24" s="14">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.162878787878</v>
+        <v>-12.420091324200</v>
       </c>
       <c r="I24" s="14">
-        <v>2507</v>
+        <v>2762</v>
       </c>
       <c r="J24" s="14">
-        <v>3119</v>
+        <v>3434</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.621673613337</v>
+        <v>-19.569015725101</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.350392230108</v>
+        <v>-5.926430517711</v>
       </c>
       <c r="M24" s="15">
-        <v>41.319052987598</v>
+        <v>42.005141388174</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D25" s="14">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E25" s="15">
-        <v>-27.647058823529</v>
+        <v>-36.746987951807</v>
       </c>
       <c r="F25" s="14">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G25" s="14">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c r="H25" s="15">
-        <v>-33.928571428571</v>
+        <v>-36.377952755905</v>
       </c>
       <c r="I25" s="14">
-        <v>1174</v>
+        <v>1279</v>
       </c>
       <c r="J25" s="14">
-        <v>1798</v>
+        <v>1964</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.705228031145</v>
+        <v>-34.877800407332</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.022889842632</v>
+        <v>-17.537072856221</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D26" s="14">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E26" s="15">
-        <v>10.810810810810</v>
+        <v>2.127659574468</v>
       </c>
       <c r="F26" s="14">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="G26" s="14">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="H26" s="15">
-        <v>4.857142857142</v>
+        <v>6.685236768802</v>
       </c>
       <c r="I26" s="14">
-        <v>985</v>
+        <v>1077</v>
       </c>
       <c r="J26" s="14">
-        <v>939</v>
+        <v>1033</v>
       </c>
       <c r="K26" s="15">
-        <v>4.898828541001</v>
+        <v>4.259438528557</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.598401598401</v>
+        <v>-2.445652173913</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.715857011915</v>
+        <v>-8.262350936967</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>4</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G27" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
-        <v>-15</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J27" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K27" s="15">
-        <v>-23.333333333333</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="L27" s="15">
-        <v>6.976744186046</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D28" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>21.428571428571</v>
+        <v>157.142857142857</v>
       </c>
       <c r="F28" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G28" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H28" s="15">
-        <v>11.111111111111</v>
+        <v>16.326530612244</v>
       </c>
       <c r="I28" s="14">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="J28" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K28" s="15">
-        <v>2.479338842975</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-2.362204724409</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>3</v>
       </c>
       <c r="E29" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>-16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>15</v>
       </c>
       <c r="J29" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K29" s="15">
-        <v>7.142857142857</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L29" s="15">
-        <v>-25</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M29" s="15">
         <v>-57.142857142857</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.477272727272</v>
+        <v>-92.227979274611</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="14">
         <v>3</v>
       </c>
-      <c r="E30" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F30" s="14">
-        <v>4</v>
-      </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I30" s="14">
         <v>13</v>
       </c>
       <c r="J30" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-18.75</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M30" s="15">
         <v>-60.606060606060</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.024539877300</v>
+        <v>-92.696629213483</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1567,16 +1567,16 @@
         <v>-12.5</v>
       </c>
       <c r="I31" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K31" s="15">
-        <v>42.857142857142</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L31" s="15">
-        <v>-13.043478260869</v>
+        <v>-16</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1608,7 +1608,7 @@
         <v>40</v>
       </c>
       <c r="C33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J33" s="14">
         <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="L33" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -870,22 +870,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="14">
         <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>-86.666666666666</v>
+        <v>-81.25</v>
       </c>
       <c r="M14" s="15">
-        <v>-83.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-97.560975609756</v>
+        <v>-96.470588235294</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F15" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G15" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="I15" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J15" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K15" s="15">
-        <v>-17.307692307692</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L15" s="15">
-        <v>48.275862068965</v>
+        <v>59.375</v>
       </c>
       <c r="M15" s="15">
-        <v>-6.521739130434</v>
+        <v>6.25</v>
       </c>
       <c r="N15" s="15">
-        <v>-59.047619047619</v>
+        <v>-56.034482758620</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E16" s="15">
-        <v>-23.333333333333</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="F16" s="14">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G16" s="14">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>1.834862385321</v>
       </c>
       <c r="I16" s="14">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="J16" s="14">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.587223587223</v>
+        <v>-22.401847575057</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.40081799591</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.977611940298</v>
+        <v>-42.068965517241</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.740486015589</v>
+        <v>-85.762711864406</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D17" s="14">
         <v>56</v>
       </c>
       <c r="E17" s="15">
-        <v>-26.785714285714</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G17" s="14">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="H17" s="15">
-        <v>1.363636363636</v>
+        <v>-3.004291845493</v>
       </c>
       <c r="I17" s="14">
-        <v>646</v>
+        <v>702</v>
       </c>
       <c r="J17" s="14">
-        <v>653</v>
+        <v>709</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.071975497702</v>
+        <v>-0.987306064880</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.238636363636</v>
+        <v>-7.509881422924</v>
       </c>
       <c r="M17" s="15">
-        <v>57.177615571776</v>
+        <v>57.752808988764</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.927536231884</v>
+        <v>-46.818181818181</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="15">
-        <v>-20.689655172413</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G18" s="14">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H18" s="15">
-        <v>-17.948717948717</v>
+        <v>-19.2</v>
       </c>
       <c r="I18" s="14">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="J18" s="14">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="K18" s="15">
-        <v>-13.483146067415</v>
+        <v>-11.917098445595</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.239436619718</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.465116279069</v>
+        <v>-7.103825136612</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.144726712856</v>
+        <v>-87.817986384808</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D19" s="14">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="E19" s="15">
-        <v>1.960784313725</v>
+        <v>-20.491803278688</v>
       </c>
       <c r="F19" s="14">
-        <v>453</v>
+        <v>414</v>
       </c>
       <c r="G19" s="14">
         <v>490</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.551020408163</v>
+        <v>-15.510204081632</v>
       </c>
       <c r="I19" s="14">
-        <v>1305</v>
+        <v>1400</v>
       </c>
       <c r="J19" s="14">
-        <v>1328</v>
+        <v>1450</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.731927710843</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.943319838056</v>
+        <v>-13.151364764268</v>
       </c>
       <c r="M19" s="15">
-        <v>26.576139670223</v>
+        <v>26.582278481012</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.803452334248</v>
+        <v>-49.256977165639</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>19</v>
+      </c>
+      <c r="D20" s="14">
         <v>12</v>
       </c>
-      <c r="D20" s="14">
-        <v>20</v>
-      </c>
       <c r="E20" s="15">
-        <v>-40</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G20" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H20" s="15">
-        <v>-29.411764705882</v>
+        <v>-23.943661971831</v>
       </c>
       <c r="I20" s="14">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="J20" s="14">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.826589595375</v>
+        <v>-6.486486486486</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.767123287671</v>
+        <v>-25.108225108225</v>
       </c>
       <c r="M20" s="15">
-        <v>57.575757575757</v>
+        <v>61.682242990654</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.229166666666</v>
+        <v>-93.043827905106</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="D21" s="17">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.807531380753</v>
+        <v>-12.350597609561</v>
       </c>
       <c r="F21" s="17">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="G21" s="17">
-        <v>1035</v>
+        <v>1045</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.275362318840</v>
+        <v>-11.387559808612</v>
       </c>
       <c r="I21" s="17">
-        <v>2771</v>
+        <v>3005</v>
       </c>
       <c r="J21" s="17">
-        <v>2975</v>
+        <v>3226</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.857142857142</v>
+        <v>-6.850588964662</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.851806863042</v>
+        <v>-15.637282425603</v>
       </c>
       <c r="M21" s="18">
-        <v>11.778943122226</v>
+        <v>12.800300300300</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.790756914119</v>
+        <v>-74.786037925826</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>6</v>
       </c>
       <c r="D22" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="14">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H22" s="15">
-        <v>-9.090909090909</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I22" s="14">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J22" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K22" s="15">
-        <v>-14.0625</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L22" s="15">
-        <v>-25.675675675675</v>
+        <v>-21.25</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>6.779661016949</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="15">
-        <v>-30.769230769230</v>
+        <v>-24</v>
       </c>
       <c r="F23" s="14">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G23" s="14">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.423076923076</v>
+        <v>-10.377358490566</v>
       </c>
       <c r="I23" s="14">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="J23" s="14">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="K23" s="15">
-        <v>-25.236593059936</v>
+        <v>-24.269005847953</v>
       </c>
       <c r="L23" s="15">
-        <v>-24.038461538461</v>
+        <v>-23.598820058997</v>
       </c>
       <c r="M23" s="15">
-        <v>22.164948453608</v>
+        <v>27.586206896551</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="D24" s="14">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="E24" s="15">
-        <v>-19.047619047619</v>
+        <v>-18.505338078291</v>
       </c>
       <c r="F24" s="14">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="G24" s="14">
-        <v>1095</v>
+        <v>1112</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.420091324200</v>
+        <v>-12.679856115107</v>
       </c>
       <c r="I24" s="14">
-        <v>2762</v>
+        <v>2991</v>
       </c>
       <c r="J24" s="14">
-        <v>3434</v>
+        <v>3715</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.569015725101</v>
+        <v>-19.488559892328</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.926430517711</v>
+        <v>-5.676442762535</v>
       </c>
       <c r="M24" s="15">
-        <v>42.005141388174</v>
+        <v>40.68673565381</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D25" s="14">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.746987951807</v>
+        <v>-36.912751677852</v>
       </c>
       <c r="F25" s="14">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G25" s="14">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.377952755905</v>
+        <v>-34.354838709677</v>
       </c>
       <c r="I25" s="14">
-        <v>1279</v>
+        <v>1373</v>
       </c>
       <c r="J25" s="14">
-        <v>1964</v>
+        <v>2113</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.877800407332</v>
+        <v>-35.021296734500</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.537072856221</v>
+        <v>-18.805440567711</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D26" s="14">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="E26" s="15">
-        <v>2.127659574468</v>
+        <v>-25.663716814159</v>
       </c>
       <c r="F26" s="14">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="G26" s="14">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="H26" s="15">
-        <v>6.685236768802</v>
+        <v>-4.021447721179</v>
       </c>
       <c r="I26" s="14">
-        <v>1077</v>
+        <v>1156</v>
       </c>
       <c r="J26" s="14">
-        <v>1033</v>
+        <v>1146</v>
       </c>
       <c r="K26" s="15">
-        <v>4.259438528557</v>
+        <v>0.872600349040</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.445652173913</v>
+        <v>-2.529510961214</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.262350936967</v>
+        <v>-6.999195494770</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F27" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H27" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J27" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K27" s="15">
-        <v>-20.634920634920</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L27" s="15">
-        <v>4.166666666666</v>
+        <v>17.647058823529</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E28" s="15">
-        <v>157.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G28" s="14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H28" s="15">
-        <v>16.326530612244</v>
+        <v>25.531914893617</v>
       </c>
       <c r="I28" s="14">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="J28" s="14">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="K28" s="15">
-        <v>12.5</v>
+        <v>9.352517985611</v>
       </c>
       <c r="L28" s="15">
-        <v>6.666666666666</v>
+        <v>4.827586206896</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,55 +1466,55 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>100</v>
+      </c>
+      <c r="F29" s="14">
         <v>3</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="I29" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J29" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>-11.764705882352</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L29" s="15">
-        <v>-34.782608695652</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M29" s="15">
-        <v>-57.142857142857</v>
+        <v>-54.054054054054</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.227979274611</v>
+        <v>-91.747572815534</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>2</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
@@ -1526,57 +1526,57 @@
         <v>-57.142857142857</v>
       </c>
       <c r="I30" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J30" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K30" s="15">
-        <v>-13.333333333333</v>
+        <v>-6.25</v>
       </c>
       <c r="L30" s="15">
-        <v>-27.777777777777</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-60.606060606060</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.696629213483</v>
+        <v>-92.146596858638</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>6</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H31" s="15">
-        <v>-12.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I31" s="14">
+        <v>26</v>
+      </c>
+      <c r="J31" s="14">
         <v>21</v>
       </c>
-      <c r="J31" s="14">
-        <v>17</v>
-      </c>
       <c r="K31" s="15">
-        <v>23.529411764705</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L31" s="15">
-        <v>-16</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,35 +1607,35 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>2</v>
-      </c>
-      <c r="D33" s="13" t="s">
+      <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
-        <v>4</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>400</v>
       </c>
       <c r="I33" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L33" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -199,67 +199,67 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
+    <t>Traffic Statistics</t>
+  </si>
+  <si>
+    <t>Traffic Fatalities</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>Traffic Statistics</t>
-  </si>
-  <si>
-    <t>Traffic Fatalities</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,617 +854,617 @@
       <c r="C14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L14" s="15">
-        <v>-81.25</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="M14" s="15">
-        <v>-75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N14" s="15">
-        <v>-96.470588235294</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>40</v>
+        <v>-25</v>
       </c>
       <c r="F15" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" s="15">
-        <v>18.75</v>
+        <v>20</v>
       </c>
       <c r="I15" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J15" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K15" s="15">
-        <v>-10.526315789473</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="L15" s="15">
-        <v>59.375</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="N15" s="15">
-        <v>-56.034482758620</v>
+        <v>-58.461538461538</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="14">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="D16" s="14">
         <v>21</v>
       </c>
-      <c r="D16" s="14">
-        <v>26</v>
-      </c>
       <c r="E16" s="15">
-        <v>-19.230769230769</v>
+        <v>9.523809523809</v>
       </c>
       <c r="F16" s="14">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G16" s="14">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H16" s="15">
-        <v>1.834862385321</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="J16" s="14">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="K16" s="15">
-        <v>-22.401847575057</v>
+        <v>-20.704845814978</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.842105263157</v>
+        <v>-36.395759717314</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.068965517241</v>
+        <v>-42.028985507246</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.762711864406</v>
+        <v>-85.680190930787</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D17" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E17" s="15">
-        <v>-19.642857142857</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G17" s="14">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.004291845493</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="I17" s="14">
-        <v>702</v>
+        <v>755</v>
       </c>
       <c r="J17" s="14">
-        <v>709</v>
+        <v>769</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.987306064880</v>
+        <v>-1.820546163849</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.509881422924</v>
+        <v>-8.706166868198</v>
       </c>
       <c r="M17" s="15">
-        <v>57.752808988764</v>
+        <v>59.282700421940</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.818181818181</v>
+        <v>-46.755994358251</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="14">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>30</v>
-      </c>
       <c r="D18" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G18" s="14">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.2</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="I18" s="14">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="J18" s="14">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.917098445595</v>
+        <v>-10.731707317073</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.526315789473</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="M18" s="15">
-        <v>-7.103825136612</v>
+        <v>-7.106598984771</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.817986384808</v>
+        <v>-87.771466755763</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D19" s="14">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E19" s="15">
-        <v>-20.491803278688</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="F19" s="14">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="G19" s="14">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.510204081632</v>
+        <v>-13.829787234042</v>
       </c>
       <c r="I19" s="14">
-        <v>1400</v>
+        <v>1497</v>
       </c>
       <c r="J19" s="14">
-        <v>1450</v>
+        <v>1555</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.448275862068</v>
+        <v>-3.729903536977</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.151364764268</v>
+        <v>-12.813046010483</v>
       </c>
       <c r="M19" s="15">
-        <v>26.582278481012</v>
+        <v>24.438902743142</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.256977165639</v>
+        <v>-49.866041527126</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D20" s="14">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E20" s="15">
-        <v>58.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="F20" s="14">
         <v>54</v>
       </c>
       <c r="G20" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H20" s="15">
-        <v>-23.943661971831</v>
+        <v>-28</v>
       </c>
       <c r="I20" s="14">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="J20" s="14">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.486486486486</v>
+        <v>-8.780487804878</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.108225108225</v>
+        <v>-23.673469387755</v>
       </c>
       <c r="M20" s="15">
-        <v>61.682242990654</v>
+        <v>53.278688524590</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.043827905106</v>
+        <v>-92.993630573248</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D21" s="17">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.350597609561</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="F21" s="17">
-        <v>926</v>
+        <v>888</v>
       </c>
       <c r="G21" s="17">
-        <v>1045</v>
+        <v>1015</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.387559808612</v>
+        <v>-12.512315270936</v>
       </c>
       <c r="I21" s="17">
-        <v>3005</v>
+        <v>3223</v>
       </c>
       <c r="J21" s="17">
-        <v>3226</v>
+        <v>3461</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.850588964662</v>
+        <v>-6.876625252817</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.637282425603</v>
+        <v>-15.406824146981</v>
       </c>
       <c r="M21" s="18">
-        <v>12.800300300300</v>
+        <v>11.987491313412</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.786037925826</v>
+        <v>-74.824246211529</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F22" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G22" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H22" s="15">
-        <v>11.111111111111</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I22" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J22" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K22" s="15">
-        <v>-4.545454545454</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-21.25</v>
+        <v>-17.283950617283</v>
       </c>
       <c r="M22" s="15">
-        <v>6.779661016949</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D23" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="15">
-        <v>-24</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F23" s="14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G23" s="14">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H23" s="15">
-        <v>-10.377358490566</v>
+        <v>-17.431192660550</v>
       </c>
       <c r="I23" s="14">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="J23" s="14">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="K23" s="15">
-        <v>-24.269005847953</v>
+        <v>-25.203252032520</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.598820058997</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="15">
-        <v>27.586206896551</v>
+        <v>28.372093023255</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D24" s="14">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.505338078291</v>
+        <v>-5.747126436781</v>
       </c>
       <c r="F24" s="14">
-        <v>971</v>
+        <v>987</v>
       </c>
       <c r="G24" s="14">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.679856115107</v>
+        <v>-12.110418521816</v>
       </c>
       <c r="I24" s="14">
-        <v>2991</v>
+        <v>3236</v>
       </c>
       <c r="J24" s="14">
-        <v>3715</v>
+        <v>3976</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.488559892328</v>
+        <v>-18.611670020120</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.676442762535</v>
+        <v>-4.739476008242</v>
       </c>
       <c r="M24" s="15">
-        <v>40.68673565381</v>
+        <v>42.366915970083</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D25" s="14">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.912751677852</v>
+        <v>-35.542168674698</v>
       </c>
       <c r="F25" s="14">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="G25" s="14">
-        <v>620</v>
+        <v>651</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.354838709677</v>
+        <v>-34.254992319508</v>
       </c>
       <c r="I25" s="14">
-        <v>1373</v>
+        <v>1478</v>
       </c>
       <c r="J25" s="14">
-        <v>2113</v>
+        <v>2279</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.021296734500</v>
+        <v>-35.146994295743</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.805440567711</v>
+        <v>-18.387631143014</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D26" s="14">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="E26" s="15">
-        <v>-25.663716814159</v>
+        <v>5.617977528089</v>
       </c>
       <c r="F26" s="14">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="G26" s="14">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H26" s="15">
-        <v>-4.021447721179</v>
+        <v>-5.675675675675</v>
       </c>
       <c r="I26" s="14">
-        <v>1156</v>
+        <v>1249</v>
       </c>
       <c r="J26" s="14">
-        <v>1146</v>
+        <v>1235</v>
       </c>
       <c r="K26" s="15">
-        <v>0.872600349040</v>
+        <v>1.133603238866</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.529510961214</v>
+        <v>-3.103180760279</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.999195494770</v>
+        <v>-6.511976047904</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>16.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F27" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I27" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J27" s="14">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K27" s="15">
-        <v>-13.043478260869</v>
+        <v>-14.864864864864</v>
       </c>
       <c r="L27" s="15">
-        <v>17.647058823529</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D28" s="14">
         <v>11</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F28" s="14">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G28" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H28" s="15">
-        <v>25.531914893617</v>
+        <v>27.906976744186</v>
       </c>
       <c r="I28" s="14">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="J28" s="14">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="K28" s="15">
-        <v>9.352517985611</v>
+        <v>8.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>4.827586206896</v>
+        <v>4.487179487179</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
         <v>2</v>
@@ -1476,36 +1476,36 @@
         <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" s="14">
         <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="I29" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J29" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K29" s="15">
-        <v>-5.555555555555</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-26.086956521739</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="M29" s="15">
-        <v>-54.054054054054</v>
+        <v>-55.813953488372</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.747572815534</v>
+        <v>-91.203703703703</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
         <v>2</v>
@@ -1517,77 +1517,77 @@
         <v>100</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
         <v>7</v>
       </c>
       <c r="H30" s="15">
-        <v>-57.142857142857</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I30" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J30" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K30" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-16.666666666666</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M30" s="15">
-        <v>-57.142857142857</v>
+        <v>-57.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.146596858638</v>
+        <v>-91.542288557213</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F31" s="14">
         <v>8</v>
       </c>
       <c r="G31" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H31" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J31" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K31" s="15">
-        <v>23.809523809523</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L31" s="15">
-        <v>-13.333333333333</v>
+        <v>-15.625</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,43 +1605,43 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F33" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I33" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L33" s="15">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>482</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>12041</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>6092</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>14267</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>13799</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>12028</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>59088</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -253,13 +253,13 @@
     <t>Hate Crimes</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Traffic Statistics</t>
   </si>
   <si>
     <t>Traffic Fatalities</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -855,37 +855,37 @@
         <v>1</v>
       </c>
       <c r="D14" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="I14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>-42.857142857142</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L14" s="15">
-        <v>-76.470588235294</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="M14" s="15">
-        <v>-71.428571428571</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.652173913043</v>
+        <v>-94.791666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F15" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H15" s="15">
-        <v>20</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I15" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J15" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K15" s="15">
-        <v>-11.475409836065</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L15" s="15">
         <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>8</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N15" s="15">
-        <v>-58.461538461538</v>
+        <v>-60.139860139860</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D16" s="14">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E16" s="15">
-        <v>9.523809523809</v>
+        <v>3.125</v>
       </c>
       <c r="F16" s="14">
         <v>103</v>
       </c>
       <c r="G16" s="14">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-5.504587155963</v>
       </c>
       <c r="I16" s="14">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="J16" s="14">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.704845814978</v>
+        <v>-19.135802469135</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.395759717314</v>
+        <v>-35.467980295566</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.028985507246</v>
+        <v>-41.343283582089</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.680190930787</v>
+        <v>-85.465976331360</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D17" s="14">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>73.913043478260</v>
       </c>
       <c r="F17" s="14">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="G17" s="14">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.638297872340</v>
+        <v>4.128440366972</v>
       </c>
       <c r="I17" s="14">
-        <v>755</v>
+        <v>841</v>
       </c>
       <c r="J17" s="14">
-        <v>769</v>
+        <v>815</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.820546163849</v>
+        <v>3.190184049079</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.706166868198</v>
+        <v>-5.292792792792</v>
       </c>
       <c r="M17" s="15">
-        <v>59.282700421940</v>
+        <v>65.225933202357</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.755994358251</v>
+        <v>-44.852459016393</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D18" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="15">
-        <v>4.166666666666</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="F18" s="14">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G18" s="14">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H18" s="15">
-        <v>-17.241379310344</v>
+        <v>-2.830188679245</v>
       </c>
       <c r="I18" s="14">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="J18" s="14">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.731707317073</v>
+        <v>-10.161662817552</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.955223880597</v>
+        <v>-9.534883720930</v>
       </c>
       <c r="M18" s="15">
-        <v>-7.106598984771</v>
+        <v>-6.038647342995</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.771466755763</v>
+        <v>-87.896701929060</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D19" s="14">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.714285714285</v>
+        <v>1.587301587301</v>
       </c>
       <c r="F19" s="14">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="G19" s="14">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.829787234042</v>
+        <v>-7.472527472527</v>
       </c>
       <c r="I19" s="14">
-        <v>1497</v>
+        <v>1622</v>
       </c>
       <c r="J19" s="14">
-        <v>1555</v>
+        <v>1681</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.729903536977</v>
+        <v>-3.509815585960</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.813046010483</v>
+        <v>-12.371690977849</v>
       </c>
       <c r="M19" s="15">
-        <v>24.438902743142</v>
+        <v>25.057825751734</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.866041527126</v>
+        <v>-49.438902743142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E20" s="15">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G20" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H20" s="15">
-        <v>-28</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I20" s="14">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="J20" s="14">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.780487804878</v>
+        <v>-13.419913419913</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.673469387755</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="M20" s="15">
-        <v>53.278688524590</v>
+        <v>48.148148148148</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.993630573248</v>
+        <v>-93.041057759220</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="D21" s="17">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.510638297872</v>
+        <v>8.108108108108</v>
       </c>
       <c r="F21" s="17">
-        <v>888</v>
+        <v>930</v>
       </c>
       <c r="G21" s="17">
-        <v>1015</v>
+        <v>984</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.512315270936</v>
+        <v>-5.487804878048</v>
       </c>
       <c r="I21" s="17">
-        <v>3223</v>
+        <v>3507</v>
       </c>
       <c r="J21" s="17">
-        <v>3461</v>
+        <v>3720</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.876625252817</v>
+        <v>-5.725806451612</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.406824146981</v>
+        <v>-14.442546962673</v>
       </c>
       <c r="M21" s="18">
-        <v>11.987491313412</v>
+        <v>13.385063045586</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.824246211529</v>
+        <v>-74.520488230165</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>27</v>
       </c>
       <c r="C22" s="14">
+        <v>7</v>
+      </c>
+      <c r="D22" s="14">
         <v>4</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
       <c r="E22" s="15">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="F22" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="15">
-        <v>38.461538461538</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I22" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J22" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>2.816901408450</v>
       </c>
       <c r="L22" s="15">
-        <v>-17.283950617283</v>
+        <v>-12.048192771084</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>2.816901408450</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>28</v>
@@ -1221,37 +1221,37 @@
         <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D23" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="15">
-        <v>-44.444444444444</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F23" s="14">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G23" s="14">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H23" s="15">
-        <v>-17.431192660550</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I23" s="14">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="J23" s="14">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="K23" s="15">
-        <v>-25.203252032520</v>
+        <v>-24.303797468354</v>
       </c>
       <c r="L23" s="15">
-        <v>-25</v>
+        <v>-22.739018087855</v>
       </c>
       <c r="M23" s="15">
-        <v>28.372093023255</v>
+        <v>31.140350877193</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>28</v>
@@ -1262,37 +1262,37 @@
         <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="D24" s="14">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.747126436781</v>
+        <v>17.5</v>
       </c>
       <c r="F24" s="14">
-        <v>987</v>
+        <v>1010</v>
       </c>
       <c r="G24" s="14">
-        <v>1123</v>
+        <v>1097</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.110418521816</v>
+        <v>-7.930720145852</v>
       </c>
       <c r="I24" s="14">
-        <v>3236</v>
+        <v>3519</v>
       </c>
       <c r="J24" s="14">
-        <v>3976</v>
+        <v>4216</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.611670020120</v>
+        <v>-16.532258064516</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.739476008242</v>
+        <v>-4.114441416893</v>
       </c>
       <c r="M24" s="15">
-        <v>42.366915970083</v>
+        <v>43.456991439054</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>28</v>
@@ -1303,34 +1303,34 @@
         <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D25" s="14">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.542168674698</v>
+        <v>1.694915254237</v>
       </c>
       <c r="F25" s="14">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G25" s="14">
-        <v>651</v>
+        <v>599</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.254992319508</v>
+        <v>-28.213689482470</v>
       </c>
       <c r="I25" s="14">
-        <v>1478</v>
+        <v>1603</v>
       </c>
       <c r="J25" s="14">
-        <v>2279</v>
+        <v>2397</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.146994295743</v>
+        <v>-33.124739257405</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.387631143014</v>
+        <v>-18.463886063072</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>28</v>
@@ -1344,37 +1344,37 @@
         <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D26" s="14">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E26" s="15">
-        <v>5.617977528089</v>
+        <v>63.013698630137</v>
       </c>
       <c r="F26" s="14">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="G26" s="14">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.675675675675</v>
+        <v>5.962059620596</v>
       </c>
       <c r="I26" s="14">
-        <v>1249</v>
+        <v>1367</v>
       </c>
       <c r="J26" s="14">
-        <v>1235</v>
+        <v>1308</v>
       </c>
       <c r="K26" s="15">
-        <v>1.133603238866</v>
+        <v>4.510703363914</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.103180760279</v>
+        <v>-1.013758146270</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.511976047904</v>
+        <v>-2.911931818181</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>28</v>
@@ -1385,34 +1385,34 @@
         <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>-40</v>
+        <v>50</v>
       </c>
       <c r="F27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G27" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
-        <v>5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I27" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J27" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.864864864864</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L27" s="15">
-        <v>10.526315789473</v>
+        <v>13.114754098360</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>28</v>
@@ -1426,34 +1426,34 @@
         <v>34</v>
       </c>
       <c r="C28" s="14">
+        <v>11</v>
+      </c>
+      <c r="D28" s="14">
         <v>12</v>
       </c>
-      <c r="D28" s="14">
-        <v>11</v>
-      </c>
       <c r="E28" s="15">
-        <v>9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G28" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H28" s="15">
-        <v>27.906976744186</v>
+        <v>17.073170731707</v>
       </c>
       <c r="I28" s="14">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="J28" s="14">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K28" s="15">
-        <v>8.666666666666</v>
+        <v>6.790123456790</v>
       </c>
       <c r="L28" s="15">
-        <v>4.487179487179</v>
+        <v>4.848484848484</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>28</v>
@@ -1467,40 +1467,40 @@
         <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G29" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>-37.5</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J29" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L29" s="15">
-        <v>-29.629629629629</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M29" s="15">
-        <v>-55.813953488372</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.203703703703</v>
+        <v>-90.393013100436</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F30" s="14">
+        <v>7</v>
+      </c>
+      <c r="G30" s="14">
         <v>5</v>
       </c>
-      <c r="G30" s="14">
-        <v>7</v>
-      </c>
       <c r="H30" s="15">
-        <v>-28.571428571428</v>
+        <v>40</v>
       </c>
       <c r="I30" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J30" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L30" s="15">
-        <v>-19.047619047619</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M30" s="15">
-        <v>-57.5</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.542288557213</v>
+        <v>-90.610328638497</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-50</v>
+      <c r="D31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G31" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H31" s="15">
-        <v>-33.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I31" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J31" s="14">
         <v>23</v>
       </c>
       <c r="K31" s="15">
-        <v>17.391304347826</v>
+        <v>34.782608695652</v>
       </c>
       <c r="L31" s="15">
-        <v>-15.625</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>28</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,25 +1605,25 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>28</v>
       </c>
       <c r="F33" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I33" s="14">
         <v>6</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>3</v>
       </c>
       <c r="G14" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H14" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I14" s="14">
         <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K14" s="15">
-        <v>-54.545454545454</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L14" s="15">
-        <v>-72.222222222222</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="M14" s="15">
-        <v>-64.285714285714</v>
+        <v>-68.75</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.791666666666</v>
+        <v>-95.049504950495</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
       <c r="E15" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="15">
-        <v>23.076923076923</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I15" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J15" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K15" s="15">
-        <v>-9.523809523809</v>
+        <v>-10.606060606060</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>51.282051282051</v>
       </c>
       <c r="M15" s="15">
-        <v>5.555555555555</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-60.139860139860</v>
+        <v>-60.927152317880</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E16" s="15">
-        <v>3.125</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G16" s="14">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H16" s="15">
-        <v>-5.504587155963</v>
+        <v>-5.217391304347</v>
       </c>
       <c r="I16" s="14">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="J16" s="14">
-        <v>486</v>
+        <v>522</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.135802469135</v>
+        <v>-18.390804597701</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.467980295566</v>
+        <v>-35.356600910470</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.343283582089</v>
+        <v>-40.502793296089</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.465976331360</v>
+        <v>-85.290055248618</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D17" s="14">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="E17" s="15">
-        <v>73.913043478260</v>
+        <v>-1.492537313432</v>
       </c>
       <c r="F17" s="14">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="G17" s="14">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="H17" s="15">
-        <v>4.128440366972</v>
+        <v>7.860262008733</v>
       </c>
       <c r="I17" s="14">
-        <v>841</v>
+        <v>906</v>
       </c>
       <c r="J17" s="14">
-        <v>815</v>
+        <v>882</v>
       </c>
       <c r="K17" s="15">
-        <v>3.190184049079</v>
+        <v>2.721088435374</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.292792792792</v>
+        <v>-4.731861198738</v>
       </c>
       <c r="M17" s="15">
-        <v>65.225933202357</v>
+        <v>65.027322404371</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.852459016393</v>
+        <v>-44.890510948905</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D18" s="14">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E18" s="15">
-        <v>-4.347826086956</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="F18" s="14">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G18" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H18" s="15">
-        <v>-2.830188679245</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="I18" s="14">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="J18" s="14">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.161662817552</v>
+        <v>-10.425531914893</v>
       </c>
       <c r="L18" s="15">
-        <v>-9.534883720930</v>
+        <v>-6.858407079646</v>
       </c>
       <c r="M18" s="15">
-        <v>-6.038647342995</v>
+        <v>-4.100227790432</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.896701929060</v>
+        <v>-87.754508435136</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D19" s="14">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E19" s="15">
-        <v>1.587301587301</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="F19" s="14">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G19" s="14">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.472527472527</v>
+        <v>-9.128630705394</v>
       </c>
       <c r="I19" s="14">
-        <v>1622</v>
+        <v>1737</v>
       </c>
       <c r="J19" s="14">
-        <v>1681</v>
+        <v>1810</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.509815585960</v>
+        <v>-4.033149171270</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.371690977849</v>
+        <v>-12.405446293494</v>
       </c>
       <c r="M19" s="15">
-        <v>25.057825751734</v>
+        <v>26.235465116279</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.438902743142</v>
+        <v>-48.715677590788</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D20" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F20" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G20" s="14">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" s="15">
-        <v>-26.923076923076</v>
+        <v>-24.050632911392</v>
       </c>
       <c r="I20" s="14">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="J20" s="14">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.419913419913</v>
+        <v>-15.079365079365</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.528301886792</v>
+        <v>-25.435540069686</v>
       </c>
       <c r="M20" s="15">
-        <v>48.148148148148</v>
+        <v>38.064516129032</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.041057759220</v>
+        <v>-93.042912873862</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="D21" s="17">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="E21" s="18">
-        <v>8.108108108108</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="F21" s="17">
-        <v>930</v>
+        <v>982</v>
       </c>
       <c r="G21" s="17">
-        <v>984</v>
+        <v>1040</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.487804878048</v>
+        <v>-5.576923076923</v>
       </c>
       <c r="I21" s="17">
-        <v>3507</v>
+        <v>3768</v>
       </c>
       <c r="J21" s="17">
-        <v>3720</v>
+        <v>4015</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.725806451612</v>
+        <v>-6.151930261519</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.442546962673</v>
+        <v>-14.168564920273</v>
       </c>
       <c r="M21" s="18">
-        <v>13.385063045586</v>
+        <v>13.836858006042</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.520488230165</v>
+        <v>-74.355135098346</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>18</v>
+      </c>
+      <c r="G22" s="14">
+        <v>12</v>
+      </c>
+      <c r="H22" s="15">
+        <v>50</v>
+      </c>
+      <c r="I22" s="14">
         <v>75</v>
       </c>
-      <c r="F22" s="14">
-        <v>16</v>
-      </c>
-      <c r="G22" s="14">
-        <v>14</v>
-      </c>
-      <c r="H22" s="15">
-        <v>14.285714285714</v>
-      </c>
-      <c r="I22" s="14">
-        <v>73</v>
-      </c>
       <c r="J22" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K22" s="15">
-        <v>2.816901408450</v>
+        <v>-1.315789473684</v>
       </c>
       <c r="L22" s="15">
-        <v>-12.048192771084</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="M22" s="15">
-        <v>2.816901408450</v>
+        <v>1.351351351351</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>20</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>77</v>
+      </c>
+      <c r="G23" s="14">
+        <v>98</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-21.428571428571</v>
+      </c>
+      <c r="I23" s="14">
+        <v>317</v>
+      </c>
+      <c r="J23" s="14">
+        <v>415</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-23.614457831325</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-22.871046228710</v>
+      </c>
+      <c r="M23" s="15">
+        <v>32.083333333333</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C23" s="14">
-        <v>22</v>
-      </c>
-      <c r="D23" s="14">
-        <v>26</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-15.384615384615</v>
-      </c>
-      <c r="F23" s="14">
-        <v>76</v>
-      </c>
-      <c r="G23" s="14">
-        <v>104</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-26.923076923076</v>
-      </c>
-      <c r="I23" s="14">
-        <v>299</v>
-      </c>
-      <c r="J23" s="14">
-        <v>395</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-24.303797468354</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-22.739018087855</v>
-      </c>
-      <c r="M23" s="15">
-        <v>31.140350877193</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="D24" s="14">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="E24" s="15">
-        <v>17.5</v>
+        <v>22.380952380952</v>
       </c>
       <c r="F24" s="14">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G24" s="14">
-        <v>1097</v>
+        <v>992</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.930720145852</v>
+        <v>1.713709677419</v>
       </c>
       <c r="I24" s="14">
-        <v>3519</v>
+        <v>3771</v>
       </c>
       <c r="J24" s="14">
-        <v>4216</v>
+        <v>4426</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.532258064516</v>
+        <v>-14.798915499322</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.114441416893</v>
+        <v>-4.265041888804</v>
       </c>
       <c r="M24" s="15">
-        <v>43.456991439054</v>
+        <v>42.624810892587</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" s="14">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E25" s="15">
-        <v>1.694915254237</v>
+        <v>-1.626016260162</v>
       </c>
       <c r="F25" s="14">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="G25" s="14">
-        <v>599</v>
+        <v>556</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.213689482470</v>
+        <v>-20.143884892086</v>
       </c>
       <c r="I25" s="14">
-        <v>1603</v>
+        <v>1722</v>
       </c>
       <c r="J25" s="14">
-        <v>2397</v>
+        <v>2520</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.124739257405</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.463886063072</v>
+        <v>-18.039029033793</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="D26" s="14">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="E26" s="15">
-        <v>63.013698630137</v>
+        <v>-27.131782945736</v>
       </c>
       <c r="F26" s="14">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G26" s="14">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="H26" s="15">
-        <v>5.962059620596</v>
+        <v>-3.465346534653</v>
       </c>
       <c r="I26" s="14">
-        <v>1367</v>
+        <v>1462</v>
       </c>
       <c r="J26" s="14">
-        <v>1308</v>
+        <v>1437</v>
       </c>
       <c r="K26" s="15">
-        <v>4.510703363914</v>
+        <v>1.739735560194</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.013758146270</v>
+        <v>-0.746775288526</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.911931818181</v>
+        <v>-3.752468729427</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>22.222222222222</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I27" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J27" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.538461538461</v>
+        <v>-13.414634146341</v>
       </c>
       <c r="L27" s="15">
-        <v>13.114754098360</v>
+        <v>10.9375</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E28" s="15">
-        <v>-8.333333333333</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F28" s="14">
+        <v>46</v>
+      </c>
+      <c r="G28" s="14">
         <v>48</v>
       </c>
-      <c r="G28" s="14">
-        <v>41</v>
-      </c>
       <c r="H28" s="15">
-        <v>17.073170731707</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J28" s="14">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="K28" s="15">
-        <v>6.790123456790</v>
+        <v>5.113636363636</v>
       </c>
       <c r="L28" s="15">
-        <v>4.848484848484</v>
+        <v>6.321839080459</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
+        <v>11</v>
+      </c>
+      <c r="G29" s="14">
         <v>7</v>
       </c>
-      <c r="G29" s="14">
-        <v>6</v>
-      </c>
       <c r="H29" s="15">
-        <v>16.666666666666</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I29" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J29" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K29" s="15">
-        <v>10</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-24.137931034482</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="M29" s="15">
-        <v>-54.166666666666</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.393013100436</v>
+        <v>-89.166666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
+        <v>4</v>
+      </c>
+      <c r="D30" s="14">
         <v>3</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
       <c r="E30" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F30" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>40</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J30" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K30" s="15">
-        <v>11.111111111111</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L30" s="15">
-        <v>-13.043478260869</v>
+        <v>-4</v>
       </c>
       <c r="M30" s="15">
-        <v>-54.545454545454</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.610328638497</v>
+        <v>-89.237668161435</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>28</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
       </c>
       <c r="F31" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G31" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31" s="15">
-        <v>22.222222222222</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J31" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K31" s="15">
-        <v>34.782608695652</v>
+        <v>37.5</v>
       </c>
       <c r="L31" s="15">
-        <v>-13.888888888888</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,40 +1608,40 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="14">
         <v>2</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
       <c r="H33" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>6</v>
       </c>
       <c r="J33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
         <v>20</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>482</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>12041</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>6092</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>14267</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>13799</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>12028</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>59088</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -855,28 +855,28 @@
         <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="15">
         <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="15">
-        <v>-57.142857142857</v>
+        <v>-75</v>
       </c>
       <c r="I14" s="14">
         <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="L14" s="15">
         <v>-73.684210526315</v>
@@ -885,7 +885,7 @@
         <v>-68.75</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.049504950495</v>
+        <v>-95.535714285714</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
         <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H15" s="15">
-        <v>7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J15" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K15" s="15">
-        <v>-10.606060606060</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L15" s="15">
-        <v>51.282051282051</v>
+        <v>46.511627906976</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>1.612903225806</v>
       </c>
       <c r="N15" s="15">
-        <v>-60.927152317880</v>
+        <v>-60.377358490566</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D16" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="F16" s="14">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G16" s="14">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="H16" s="15">
-        <v>-5.217391304347</v>
+        <v>-4.724409448818</v>
       </c>
       <c r="I16" s="14">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="J16" s="14">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.390804597701</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.356600910470</v>
+        <v>-33.908045977011</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.502793296089</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.290055248618</v>
+        <v>-84.952567877003</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
+        <v>67</v>
+      </c>
+      <c r="D17" s="14">
         <v>66</v>
       </c>
-      <c r="D17" s="14">
-        <v>67</v>
-      </c>
       <c r="E17" s="15">
-        <v>-1.492537313432</v>
+        <v>1.515151515151</v>
       </c>
       <c r="F17" s="14">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="G17" s="14">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="H17" s="15">
-        <v>7.860262008733</v>
+        <v>11.715481171548</v>
       </c>
       <c r="I17" s="14">
-        <v>906</v>
+        <v>976</v>
       </c>
       <c r="J17" s="14">
-        <v>882</v>
+        <v>948</v>
       </c>
       <c r="K17" s="15">
-        <v>2.721088435374</v>
+        <v>2.953586497890</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.731861198738</v>
+        <v>-4.780487804878</v>
       </c>
       <c r="M17" s="15">
-        <v>65.027322404371</v>
+        <v>67.123287671232</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.890510948905</v>
+        <v>-44.068767908309</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E18" s="15">
-        <v>-18.918918918918</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G18" s="14">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H18" s="15">
-        <v>-3.508771929824</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="J18" s="14">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.425531914893</v>
+        <v>-9.164969450101</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.858407079646</v>
+        <v>-7.660455486542</v>
       </c>
       <c r="M18" s="15">
-        <v>-4.100227790432</v>
+        <v>-3.253796095444</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.754508435136</v>
+        <v>-87.787513691128</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D19" s="14">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.302325581395</v>
+        <v>-20.270270270270</v>
       </c>
       <c r="F19" s="14">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="G19" s="14">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.128630705394</v>
+        <v>-9.448818897637</v>
       </c>
       <c r="I19" s="14">
-        <v>1737</v>
+        <v>1856</v>
       </c>
       <c r="J19" s="14">
-        <v>1810</v>
+        <v>1958</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.033149171270</v>
+        <v>-5.209397344228</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.405446293494</v>
+        <v>-12.162801703738</v>
       </c>
       <c r="M19" s="15">
-        <v>26.235465116279</v>
+        <v>26.516700749829</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.715677590788</v>
+        <v>-48.315232525758</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E20" s="15">
-        <v>-28.571428571428</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F20" s="14">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G20" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H20" s="15">
-        <v>-24.050632911392</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="J20" s="14">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.079365079365</v>
+        <v>-17.100371747211</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.435540069686</v>
+        <v>-24.662162162162</v>
       </c>
       <c r="M20" s="15">
-        <v>38.064516129032</v>
+        <v>31.176470588235</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.042912873862</v>
+        <v>-93.199146081122</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D21" s="17">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.864406779661</v>
+        <v>-13.265306122449</v>
       </c>
       <c r="F21" s="17">
-        <v>982</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="17">
-        <v>1040</v>
+        <v>1083</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.576923076923</v>
+        <v>-6.278855032317</v>
       </c>
       <c r="I21" s="17">
-        <v>3768</v>
+        <v>4029</v>
       </c>
       <c r="J21" s="17">
-        <v>4015</v>
+        <v>4309</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.151930261519</v>
+        <v>-6.498027384543</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.168564920273</v>
+        <v>-13.818181818181</v>
       </c>
       <c r="M21" s="18">
-        <v>13.836858006042</v>
+        <v>14.460227272727</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.355135098346</v>
+        <v>-74.164796409105</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F22" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G22" s="14">
         <v>12</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="I22" s="14">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J22" s="14">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K22" s="15">
-        <v>-1.315789473684</v>
+        <v>6.410256410256</v>
       </c>
       <c r="L22" s="15">
-        <v>-13.793103448275</v>
+        <v>-6.741573033707</v>
       </c>
       <c r="M22" s="15">
-        <v>1.351351351351</v>
+        <v>7.792207792207</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D23" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>4.347826086956</v>
       </c>
       <c r="F23" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G23" s="14">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H23" s="15">
-        <v>-21.428571428571</v>
+        <v>-14.583333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="J23" s="14">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="K23" s="15">
-        <v>-23.614457831325</v>
+        <v>-22.146118721461</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.871046228710</v>
+        <v>-21.967963386727</v>
       </c>
       <c r="M23" s="15">
-        <v>32.083333333333</v>
+        <v>32.684824902723</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D24" s="14">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="E24" s="15">
-        <v>22.380952380952</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="G24" s="14">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H24" s="15">
-        <v>1.713709677419</v>
+        <v>2.316213494461</v>
       </c>
       <c r="I24" s="14">
-        <v>3771</v>
+        <v>3999</v>
       </c>
       <c r="J24" s="14">
-        <v>4426</v>
+        <v>4708</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.798915499322</v>
+        <v>-15.059473237043</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.265041888804</v>
+        <v>-4.192620987062</v>
       </c>
       <c r="M24" s="15">
-        <v>42.624810892587</v>
+        <v>41.959531416400</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D25" s="14">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="E25" s="15">
-        <v>-1.626016260162</v>
+        <v>-6.569343065693</v>
       </c>
       <c r="F25" s="14">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="G25" s="14">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.143884892086</v>
+        <v>-11.580882352941</v>
       </c>
       <c r="I25" s="14">
-        <v>1722</v>
+        <v>1851</v>
       </c>
       <c r="J25" s="14">
-        <v>2520</v>
+        <v>2657</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.666666666666</v>
+        <v>-30.334964245389</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.039029033793</v>
+        <v>-16.808988764044</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D26" s="14">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E26" s="15">
-        <v>-27.131782945736</v>
+        <v>-35.833333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G26" s="14">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.465346534653</v>
+        <v>-6.082725060827</v>
       </c>
       <c r="I26" s="14">
-        <v>1462</v>
+        <v>1540</v>
       </c>
       <c r="J26" s="14">
-        <v>1437</v>
+        <v>1557</v>
       </c>
       <c r="K26" s="15">
-        <v>1.739735560194</v>
+        <v>-1.091843288375</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.746775288526</v>
+        <v>-1.910828025477</v>
       </c>
       <c r="M26" s="15">
-        <v>-3.752468729427</v>
+        <v>-7.396271797955</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
         <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G27" s="14">
         <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>-5.263157894736</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I27" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J27" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K27" s="15">
-        <v>-13.414634146341</v>
+        <v>-14.772727272727</v>
       </c>
       <c r="L27" s="15">
-        <v>10.9375</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E28" s="15">
-        <v>-7.142857142857</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G28" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H28" s="15">
-        <v>-4.166666666666</v>
+        <v>4.081632653061</v>
       </c>
       <c r="I28" s="14">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J28" s="14">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="K28" s="15">
-        <v>5.113636363636</v>
+        <v>6.382978723404</v>
       </c>
       <c r="L28" s="15">
-        <v>6.321839080459</v>
+        <v>4.712041884816</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
         <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
+        <v>29</v>
+      </c>
+      <c r="J29" s="14">
         <v>26</v>
       </c>
-      <c r="J29" s="14">
-        <v>24</v>
-      </c>
       <c r="K29" s="15">
-        <v>8.333333333333</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L29" s="15">
-        <v>-16.129032258064</v>
+        <v>-9.375</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-49.122807017543</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.166666666666</v>
+        <v>-88.492063492063</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,75 +1508,75 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>11</v>
       </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="15">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I30" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J30" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K30" s="15">
-        <v>14.285714285714</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L30" s="15">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.237668161435</v>
+        <v>-88.936170212766</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
         <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G31" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I31" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J31" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K31" s="15">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="L31" s="15">
-        <v>-15.384615384615</v>
+        <v>-15</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1607,35 +1607,35 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14">
+        <v>2</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
+      <c r="E33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="14">
+        <v>2</v>
+      </c>
+      <c r="G33" s="14">
         <v>1</v>
       </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="14">
-        <v>2</v>
-      </c>
       <c r="H33" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I33" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J33" s="14">
         <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L33" s="15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>29</v>

--- a/data/source/weekly/cs-en-us-pbmn.xlsx
+++ b/data/source/weekly/cs-en-us-pbmn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="14">
-        <v>2</v>
-      </c>
       <c r="G14" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" s="15">
-        <v>-75</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I14" s="14">
         <v>5</v>
@@ -882,338 +882,338 @@
         <v>-73.684210526315</v>
       </c>
       <c r="M14" s="15">
-        <v>-68.75</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.535714285714</v>
+        <v>-95.798319327731</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F15" s="14">
         <v>12</v>
       </c>
       <c r="G15" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H15" s="15">
+        <v>20</v>
+      </c>
+      <c r="I15" s="14">
+        <v>66</v>
+      </c>
+      <c r="J15" s="14">
+        <v>71</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-7.042253521126</v>
+      </c>
+      <c r="L15" s="15">
+        <v>37.5</v>
+      </c>
+      <c r="M15" s="15">
         <v>0</v>
       </c>
-      <c r="I15" s="14">
-        <v>63</v>
-      </c>
-      <c r="J15" s="14">
-        <v>69</v>
-      </c>
-      <c r="K15" s="15">
-        <v>-8.695652173913</v>
-      </c>
-      <c r="L15" s="15">
-        <v>46.511627906976</v>
-      </c>
-      <c r="M15" s="15">
-        <v>1.612903225806</v>
-      </c>
       <c r="N15" s="15">
-        <v>-60.377358490566</v>
+        <v>-60.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D16" s="14">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E16" s="15">
-        <v>-13.157894736842</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G16" s="14">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H16" s="15">
-        <v>-4.724409448818</v>
+        <v>-6.153846153846</v>
       </c>
       <c r="I16" s="14">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="J16" s="14">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="K16" s="15">
-        <v>-17.857142857142</v>
+        <v>-16.952054794520</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.908045977011</v>
+        <v>-34.459459459459</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.473684210526</v>
+        <v>-39.375</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.952567877003</v>
+        <v>-85.127261576203</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="D17" s="14">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="15">
-        <v>1.515151515151</v>
+        <v>-33.846153846153</v>
       </c>
       <c r="F17" s="14">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="G17" s="14">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H17" s="15">
-        <v>11.715481171548</v>
+        <v>5.349794238683</v>
       </c>
       <c r="I17" s="14">
-        <v>976</v>
+        <v>1021</v>
       </c>
       <c r="J17" s="14">
-        <v>948</v>
+        <v>1012</v>
       </c>
       <c r="K17" s="15">
-        <v>2.953586497890</v>
+        <v>0.889328063241</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.780487804878</v>
+        <v>-6.672760511883</v>
       </c>
       <c r="M17" s="15">
-        <v>67.123287671232</v>
+        <v>63.621794871794</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.068767908309</v>
+        <v>-44.929881337648</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <v>24</v>
       </c>
       <c r="D18" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E18" s="15">
-        <v>14.285714285714</v>
+        <v>26.315789473684</v>
       </c>
       <c r="F18" s="14">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G18" s="14">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H18" s="15">
-        <v>-2.857142857142</v>
+        <v>-2</v>
       </c>
       <c r="I18" s="14">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="J18" s="14">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="K18" s="15">
-        <v>-9.164969450101</v>
+        <v>-8.235294117647</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.660455486542</v>
+        <v>-6.4</v>
       </c>
       <c r="M18" s="15">
-        <v>-3.253796095444</v>
+        <v>-3.505154639175</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.787513691128</v>
+        <v>-87.844155844155</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>108</v>
+      </c>
+      <c r="D19" s="14">
         <v>118</v>
       </c>
-      <c r="D19" s="14">
-        <v>148</v>
-      </c>
       <c r="E19" s="15">
-        <v>-20.270270270270</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="F19" s="14">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="G19" s="14">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.448818897637</v>
+        <v>-9.021113243762</v>
       </c>
       <c r="I19" s="14">
-        <v>1856</v>
+        <v>1969</v>
       </c>
       <c r="J19" s="14">
-        <v>1958</v>
+        <v>2076</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.209397344228</v>
+        <v>-5.154142581888</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.162801703738</v>
+        <v>-10.945273631840</v>
       </c>
       <c r="M19" s="15">
-        <v>26.516700749829</v>
+        <v>25.654116145501</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.315232525758</v>
+        <v>-47.827239003709</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D20" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E20" s="15">
-        <v>-41.176470588235</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F20" s="14">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G20" s="14">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H20" s="15">
-        <v>-39.285714285714</v>
+        <v>-42.352941176470</v>
       </c>
       <c r="I20" s="14">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="J20" s="14">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.100371747211</v>
+        <v>-18.620689655172</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.662162162162</v>
+        <v>-24.358974358974</v>
       </c>
       <c r="M20" s="15">
-        <v>31.176470588235</v>
+        <v>27.567567567567</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.199146081122</v>
+        <v>-93.123543123543</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="D21" s="17">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.265306122449</v>
+        <v>-11.244979919678</v>
       </c>
       <c r="F21" s="17">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="G21" s="17">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.278855032317</v>
+        <v>-7.664233576642</v>
       </c>
       <c r="I21" s="17">
-        <v>4029</v>
+        <v>4250</v>
       </c>
       <c r="J21" s="17">
-        <v>4309</v>
+        <v>4557</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.498027384543</v>
+        <v>-6.736888303708</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.818181818181</v>
+        <v>-13.688058489033</v>
       </c>
       <c r="M21" s="18">
-        <v>14.460227272727</v>
+        <v>13.514957264957</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.164796409105</v>
+        <v>-74.176692186170</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
+        <v>23</v>
+      </c>
+      <c r="G22" s="14">
+        <v>15</v>
+      </c>
+      <c r="H22" s="15">
+        <v>53.333333333333</v>
+      </c>
+      <c r="I22" s="14">
+        <v>87</v>
+      </c>
+      <c r="J22" s="14">
+        <v>82</v>
+      </c>
+      <c r="K22" s="15">
+        <v>6.097560975609</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-7.446808510638</v>
+      </c>
+      <c r="M22" s="15">
+        <v>3.571428571428</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="G22" s="14">
-        <v>12</v>
-      </c>
-      <c r="H22" s="15">
-        <v>75</v>
-      </c>
-      <c r="I22" s="14">
-        <v>83</v>
-      </c>
-      <c r="J22" s="14">
-        <v>78</v>
-      </c>
-      <c r="K22" s="15">
-        <v>6.410256410256</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-6.741573033707</v>
-      </c>
-      <c r="M22" s="15">
-        <v>7.792207792207</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" s="15">
-        <v>4.347826086956</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F23" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G23" s="14">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.583333333333</v>
+        <v>-3.296703296703</v>
       </c>
       <c r="I23" s="14">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="J23" s="14">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="K23" s="15">
-        <v>-22.146118721461</v>
+        <v>-21.086956521739</v>
       </c>
       <c r="L23" s="15">
-        <v>-21.967963386727</v>
+        <v>-21.767241379310</v>
       </c>
       <c r="M23" s="15">
-        <v>32.684824902723</v>
+        <v>32.481751824817</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="D24" s="14">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>-3.007518796992</v>
       </c>
       <c r="F24" s="14">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="G24" s="14">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="H24" s="15">
-        <v>2.316213494461</v>
+        <v>3.306613226452</v>
       </c>
       <c r="I24" s="14">
-        <v>3999</v>
+        <v>4256</v>
       </c>
       <c r="J24" s="14">
-        <v>4708</v>
+        <v>4974</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.059473237043</v>
+        <v>-14.435062324085</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.192620987062</v>
+        <v>-3.052391799544</v>
       </c>
       <c r="M24" s="15">
-        <v>41.959531416400</v>
+        <v>41.301460823373</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D25" s="14">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.569343065693</v>
+        <v>-15.079365079365</v>
       </c>
       <c r="F25" s="14">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="G25" s="14">
-        <v>544</v>
+        <v>504</v>
       </c>
       <c r="H25" s="15">
-        <v>-11.580882352941</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I25" s="14">
-        <v>1851</v>
+        <v>1958</v>
       </c>
       <c r="J25" s="14">
-        <v>2657</v>
+        <v>2783</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.334964245389</v>
+        <v>-29.644268774703</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.808988764044</v>
+        <v>-16.360529688167</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="D26" s="14">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E26" s="15">
-        <v>-35.833333333333</v>
+        <v>1.801801801801</v>
       </c>
       <c r="F26" s="14">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="G26" s="14">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.082725060827</v>
+        <v>-5.760368663594</v>
       </c>
       <c r="I26" s="14">
-        <v>1540</v>
+        <v>1657</v>
       </c>
       <c r="J26" s="14">
-        <v>1557</v>
+        <v>1669</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.091843288375</v>
+        <v>-0.718993409227</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.910828025477</v>
+        <v>-1.192605843768</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.396271797955</v>
+        <v>-6.012478729438</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>4</v>
+      </c>
+      <c r="D27" s="14">
         <v>3</v>
       </c>
-      <c r="D27" s="14">
-        <v>6</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G27" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H27" s="15">
-        <v>-21.052631578947</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I27" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J27" s="14">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.772727272727</v>
+        <v>-13.186813186813</v>
       </c>
       <c r="L27" s="15">
-        <v>7.142857142857</v>
+        <v>3.947368421052</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E28" s="15">
-        <v>16.666666666666</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F28" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G28" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H28" s="15">
-        <v>4.081632653061</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="I28" s="14">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="J28" s="14">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="K28" s="15">
-        <v>6.382978723404</v>
+        <v>4.878048780487</v>
       </c>
       <c r="L28" s="15">
-        <v>4.712041884816</v>
+        <v>7.5</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
         <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29" s="14">
         <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="I29" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J29" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K29" s="15">
-        <v>11.538461538461</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L29" s="15">
-        <v>-9.375</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-49.122807017543</v>
+        <v>-49.152542372881</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.492063492063</v>
+        <v>-88.805970149253</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,81 +1508,81 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30" s="14">
         <v>7</v>
       </c>
       <c r="H30" s="15">
-        <v>57.142857142857</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I30" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J30" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K30" s="15">
-        <v>13.043478260869</v>
+        <v>12.5</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M30" s="15">
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.936170212766</v>
+        <v>-89.112903225806</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J31" s="14">
         <v>25</v>
       </c>
       <c r="K31" s="15">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L31" s="15">
-        <v>-15</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>2</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>2</v>
@@ -1638,10 +1638,10 @@
         <v>60</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>482</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>12041</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>6092</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>14267</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>13799</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>12028</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>59088</v>
